--- a/data/CS7/case33_2/case33_2_operational_data.xlsx
+++ b/data/CS7/case33_2/case33_2_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD647E4C-9715-4C6A-81B7-2D19023D2313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EFD6A9-1237-40B3-B059-81B55DBC9170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72810" yWindow="-10815" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17925" yWindow="-17595" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="23">
   <si>
     <t>Type</t>
   </si>
@@ -109,6 +109,12 @@
   <si>
     <t>Flexible Load</t>
   </si>
+  <si>
+    <t>Pc_</t>
+  </si>
+  <si>
+    <t>Qc_</t>
+  </si>
 </sst>
 </file>
 
@@ -123,12 +129,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -143,10 +155,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,14 +440,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B7BE64-82AA-46B6-895E-9570C0781B75}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -447,460 +460,722 @@
       <c r="D1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
+        <f>E2*1</f>
         <v>3.1</v>
       </c>
       <c r="C2" s="1">
-        <v>-2.4</v>
+        <f>F2*1.25</f>
+        <v>-3</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1">
+        <f t="shared" ref="B3:B33" si="0">E3*1</f>
         <v>4.7699999999999996</v>
       </c>
       <c r="C3" s="1">
-        <v>0.6</v>
+        <f t="shared" ref="C3:C33" si="1">F3*1.25</f>
+        <v>0.75</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="3">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1">
+        <f t="shared" si="0"/>
         <v>4.4399999999999995</v>
       </c>
       <c r="C4" s="1">
-        <v>-2.48</v>
+        <f t="shared" si="1"/>
+        <v>-3.1</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="3">
+        <v>4.4399999999999995</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1">
+        <f t="shared" si="0"/>
         <v>2.04</v>
       </c>
       <c r="C5" s="1">
-        <v>0.3</v>
+        <f t="shared" si="1"/>
+        <v>0.375</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1">
+        <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
       <c r="C6" s="1">
-        <v>0.24</v>
+        <f t="shared" si="1"/>
+        <v>0.3</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>-2.2000000000000002</v>
+        <f t="shared" si="1"/>
+        <v>-2.75</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1">
+        <f t="shared" si="0"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="C8" s="1">
-        <v>-2.2000000000000002</v>
+        <f t="shared" si="1"/>
+        <v>-2.75</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1">
+        <f t="shared" si="0"/>
         <v>1.26</v>
       </c>
       <c r="C9" s="1">
-        <v>0.3</v>
+        <f t="shared" si="1"/>
+        <v>0.375</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="3">
+        <v>1.26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1">
+        <f t="shared" si="0"/>
         <v>1.26</v>
       </c>
       <c r="C10" s="1">
-        <v>-0.62</v>
+        <f t="shared" si="1"/>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="3">
+        <v>1.26</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="1">
+        <f t="shared" si="0"/>
         <v>2.0699999999999998</v>
       </c>
       <c r="C11" s="1">
-        <v>0.12</v>
+        <f t="shared" si="1"/>
+        <v>0.15</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="3">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="1">
+        <f t="shared" si="0"/>
         <v>2.82</v>
       </c>
       <c r="C12" s="1">
-        <v>-1.2250000000000001</v>
+        <f t="shared" si="1"/>
+        <v>-1.53125</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="3">
+        <v>2.82</v>
+      </c>
+      <c r="F12" s="3">
+        <v>-1.2250000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="1">
+        <f t="shared" si="0"/>
         <v>2.2799999999999998</v>
       </c>
       <c r="C13" s="1">
-        <v>-1.05</v>
+        <f t="shared" si="1"/>
+        <v>-1.3125</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="3">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="1">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C14" s="1">
-        <v>-0.88</v>
+        <f t="shared" si="1"/>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="3">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="1">
+        <f t="shared" si="0"/>
         <v>2.88</v>
       </c>
       <c r="C15" s="1">
-        <v>-0.04</v>
+        <f t="shared" si="1"/>
+        <v>-0.05</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="1">
+        <f t="shared" si="0"/>
         <v>2.6399999999999997</v>
       </c>
       <c r="C16" s="1">
-        <v>0.76</v>
+        <f t="shared" si="1"/>
+        <v>0.95</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="3">
+        <v>2.6399999999999997</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1">
+        <f t="shared" si="0"/>
         <v>2.04</v>
       </c>
       <c r="C17" s="1">
-        <v>0.76</v>
+        <f t="shared" si="1"/>
+        <v>0.95</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="1">
+        <f t="shared" si="0"/>
         <v>5.22</v>
       </c>
       <c r="C18" s="1">
-        <v>1.08</v>
+        <f t="shared" si="1"/>
+        <v>1.35</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="3">
+        <v>5.22</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="1">
+        <f t="shared" si="0"/>
         <v>1.89</v>
       </c>
       <c r="C19" s="1">
-        <v>0.84</v>
+        <f t="shared" si="1"/>
+        <v>1.05</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="3">
+        <v>1.89</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="1">
+        <f t="shared" si="0"/>
         <v>3.78</v>
       </c>
       <c r="C20" s="1">
-        <v>-1.04</v>
+        <f t="shared" si="1"/>
+        <v>-1.3</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="3">
+        <v>3.78</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="1">
+        <f t="shared" si="0"/>
         <v>3.69</v>
       </c>
       <c r="C21" s="1">
-        <v>-1.44</v>
+        <f t="shared" si="1"/>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="1">
+        <f t="shared" si="0"/>
         <v>2.79</v>
       </c>
       <c r="C22" s="1">
-        <v>-0.12</v>
+        <f t="shared" si="1"/>
+        <v>-0.15</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="F22" s="3">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="1">
+        <f t="shared" si="0"/>
         <v>3.33</v>
       </c>
       <c r="C23" s="1">
-        <v>1.4500000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.8125000000000002</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1.4500000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="1">
+        <f t="shared" si="0"/>
         <v>11.34</v>
       </c>
       <c r="C24" s="1">
-        <v>-0.4</v>
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="3">
+        <v>11.34</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="1">
+        <f t="shared" si="0"/>
         <v>15.12</v>
       </c>
       <c r="C25" s="1">
-        <v>6.4</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="3">
+        <v>15.12</v>
+      </c>
+      <c r="F25" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="1">
+        <f t="shared" si="0"/>
         <v>1.3199999999999998</v>
       </c>
       <c r="C26" s="1">
-        <v>0.92500000000000004</v>
+        <f t="shared" si="1"/>
+        <v>1.15625</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="3">
+        <v>1.3199999999999998</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="1">
+        <f t="shared" si="0"/>
         <v>2.46</v>
       </c>
       <c r="C27" s="1">
-        <v>-0.55000000000000004</v>
+        <f t="shared" si="1"/>
+        <v>-0.6875</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" s="3">
+        <v>2.46</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="1">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C28" s="1">
-        <v>-0.8</v>
+        <f t="shared" si="1"/>
+        <v>-1</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" s="3">
+        <v>3</v>
+      </c>
+      <c r="F28" s="3">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="1">
+        <f t="shared" si="0"/>
         <v>5.64</v>
       </c>
       <c r="C29" s="1">
-        <v>0.42000000000000004</v>
+        <f t="shared" si="1"/>
+        <v>0.52500000000000002</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="3">
+        <v>5.64</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0.42000000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="1">
+        <f t="shared" si="0"/>
         <v>6.2</v>
       </c>
       <c r="C30" s="1">
-        <v>-12.6</v>
+        <f t="shared" si="1"/>
+        <v>-15.75</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="F30" s="3">
+        <v>-12.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="1">
+        <f t="shared" si="0"/>
         <v>7.6499999999999995</v>
       </c>
       <c r="C31" s="1">
-        <v>0.77</v>
+        <f t="shared" si="1"/>
+        <v>0.96250000000000002</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" s="3">
+        <v>7.6499999999999995</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="1">
+        <f t="shared" si="0"/>
         <v>9.0299999999999994</v>
       </c>
       <c r="C32" s="1">
-        <v>1.7000000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.125</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" s="3">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1.7000000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="1">
+        <f t="shared" si="0"/>
         <v>2.04</v>
       </c>
       <c r="C33" s="1">
-        <v>0.16</v>
+        <f t="shared" si="1"/>
+        <v>0.2</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>

--- a/data/CS7/case33_2/case33_2_operational_data.xlsx
+++ b/data/CS7/case33_2/case33_2_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EFD6A9-1237-40B3-B059-81B55DBC9170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82671D14-2BB4-4AE1-A678-B201490C82BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17925" yWindow="-17595" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -1092,8 +1092,7 @@
         <v>6.2</v>
       </c>
       <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>-15.75</v>
+        <v>-3</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>

--- a/data/CS7/case33_2/case33_2_operational_data.xlsx
+++ b/data/CS7/case33_2/case33_2_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564BAD3D-9DF4-40D1-933F-6AA7F4359552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A091343-973F-401E-94AF-72B68D144003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -476,8 +476,8 @@
         <v>3.1</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*1.25</f>
-        <v>-3</v>
+        <f>F2*1.2</f>
+        <v>-2.88</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -498,8 +498,8 @@
         <v>4.7699999999999996</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*1.25</f>
-        <v>0.75</v>
+        <f t="shared" ref="C3:C33" si="1">F3*1.2</f>
+        <v>0.72</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -521,7 +521,7 @@
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>-3.1</v>
+        <v>-2.976</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -543,7 +543,7 @@
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.36</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -565,7 +565,7 @@
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -587,7 +587,7 @@
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>-2.75</v>
+        <v>-2.64</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -609,7 +609,7 @@
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>-2.75</v>
+        <v>-2.64</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.36</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>-0.77500000000000002</v>
+        <v>-0.74399999999999999</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -675,7 +675,7 @@
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>0.15</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -697,7 +697,7 @@
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>-1.53125</v>
+        <v>-1.47</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -719,7 +719,7 @@
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>-1.3125</v>
+        <v>-1.26</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -741,7 +741,7 @@
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>-1.1000000000000001</v>
+        <v>-1.056</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>-0.05</v>
+        <v>-4.8000000000000001E-2</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -785,7 +785,7 @@
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>0.95</v>
+        <v>0.91199999999999992</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>0.95</v>
+        <v>0.91199999999999992</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>1.35</v>
+        <v>1.296</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -851,7 +851,7 @@
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>1.05</v>
+        <v>1.008</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>-1.3</v>
+        <v>-1.248</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>-1.7999999999999998</v>
+        <v>-1.728</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>-0.15</v>
+        <v>-0.14399999999999999</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -939,7 +939,7 @@
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>1.8125000000000002</v>
+        <v>1.7400000000000002</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -961,7 +961,7 @@
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7.68</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>1.15625</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>-0.6875</v>
+        <v>-0.66</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>0.52500000000000002</v>
+        <v>0.504</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1092,7 +1092,7 @@
         <v>6.2</v>
       </c>
       <c r="C30" s="1">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>0.96250000000000002</v>
+        <v>0.92399999999999993</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C32" s="1">
         <f t="shared" si="1"/>
-        <v>2.125</v>
+        <v>2.04</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C33" s="1">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.192</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>

--- a/data/CS7/case33_2/case33_2_operational_data.xlsx
+++ b/data/CS7/case33_2/case33_2_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A091343-973F-401E-94AF-72B68D144003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5724485A-8EC0-4435-9E80-D85EA66684E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -956,12 +956,12 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>11.34</v>
+        <f>E24*0.5</f>
+        <v>5.67</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.48</v>
+        <f>F24*10</f>
+        <v>-4</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -978,8 +978,8 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>15.12</v>
+        <f>E25*0.5</f>
+        <v>7.56</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
@@ -1109,12 +1109,12 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>7.6499999999999995</v>
+        <f>E31*0.5</f>
+        <v>3.8249999999999997</v>
       </c>
       <c r="C31" s="1">
-        <f t="shared" si="1"/>
-        <v>0.92399999999999993</v>
+        <f>F31*3</f>
+        <v>2.31</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1131,12 +1131,12 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <f t="shared" si="0"/>
-        <v>9.0299999999999994</v>
+        <f>E32*0.5</f>
+        <v>4.5149999999999997</v>
       </c>
       <c r="C32" s="1">
-        <f t="shared" si="1"/>
-        <v>2.04</v>
+        <f>F32*3</f>
+        <v>5.1000000000000005</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>

--- a/data/CS7/case33_2/case33_2_operational_data.xlsx
+++ b/data/CS7/case33_2/case33_2_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5724485A-8EC0-4435-9E80-D85EA66684E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0B848D-81D8-44D4-97FD-219CE3AF7A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="74130" yWindow="-11970" windowWidth="23250" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -472,12 +472,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*1</f>
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*1.2</f>
-        <v>-2.88</v>
+        <v>2.88</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -494,12 +492,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*1</f>
-        <v>4.7699999999999996</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*1.2</f>
-        <v>0.72</v>
+        <v>1.92</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -516,12 +512,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>4.4399999999999995</v>
+        <v>4.8</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" si="1"/>
-        <v>-2.976</v>
+        <v>3.84</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -538,12 +532,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" si="1"/>
-        <v>0.36</v>
+        <v>1.44</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -560,12 +552,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="C6" s="1">
-        <f t="shared" si="1"/>
-        <v>0.28799999999999998</v>
+        <v>0.96</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -582,12 +572,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" si="1"/>
-        <v>-2.64</v>
+        <v>4.8</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -604,12 +592,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>4.4000000000000004</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="1"/>
-        <v>-2.64</v>
+        <v>4.8</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -626,12 +612,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" si="1"/>
-        <v>0.36</v>
+        <v>0.96</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -648,12 +632,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.74399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -670,12 +652,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0699999999999998</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" si="1"/>
-        <v>0.14399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -692,12 +672,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="C12" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.47</v>
+        <v>1.6800000000000002</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -714,12 +692,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>2.2799999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C13" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.26</v>
+        <v>1.6800000000000002</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -736,12 +712,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.056</v>
+        <v>3.84</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -758,12 +732,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.8000000000000001E-2</v>
+        <v>0.48</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -780,12 +752,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>2.6399999999999997</v>
+        <v>2.4</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" si="1"/>
-        <v>0.91199999999999992</v>
+        <v>0.96</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -802,12 +772,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" si="1"/>
-        <v>0.91199999999999992</v>
+        <v>0.96</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -824,12 +792,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>5.22</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" si="1"/>
-        <v>1.296</v>
+        <v>1.92</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -846,12 +812,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>1.89</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="1"/>
-        <v>1.008</v>
+        <v>1.92</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -868,12 +832,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>3.78</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.248</v>
+        <v>1.92</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -890,12 +852,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>3.69</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C21" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.728</v>
+        <v>1.92</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -912,12 +872,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>2.79</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.14399999999999999</v>
+        <v>1.92</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -934,12 +892,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" si="1"/>
-        <v>1.7400000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -956,12 +912,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <f>E24*0.5</f>
-        <v>5.67</v>
+        <v>16.8</v>
       </c>
       <c r="C24" s="1">
-        <f>F24*10</f>
-        <v>-4</v>
+        <v>9.6</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -978,12 +932,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <f>E25*0.5</f>
-        <v>7.56</v>
+        <v>16.8</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>7.68</v>
+        <v>9.6</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1000,12 +952,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <f t="shared" si="0"/>
-        <v>1.3199999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>1.1100000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1022,12 +972,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <f t="shared" si="0"/>
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="C27" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.66</v>
+        <v>1.2</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1044,12 +992,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.96</v>
+        <v>0.96</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1066,12 +1012,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <f t="shared" si="0"/>
-        <v>5.64</v>
+        <v>4.8</v>
       </c>
       <c r="C29" s="1">
-        <f t="shared" si="1"/>
-        <v>0.504</v>
+        <v>3.3600000000000003</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1088,11 +1032,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1109,12 +1052,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <f>E31*0.5</f>
-        <v>3.8249999999999997</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1">
-        <f>F31*3</f>
-        <v>2.31</v>
+        <v>3.3600000000000003</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1131,12 +1072,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <f>E32*0.5</f>
-        <v>4.5149999999999997</v>
+        <v>8.4</v>
       </c>
       <c r="C32" s="1">
-        <f>F32*3</f>
-        <v>5.1000000000000005</v>
+        <v>4.8</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1153,12 +1092,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <f t="shared" si="0"/>
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="C33" s="1">
-        <f t="shared" si="1"/>
-        <v>0.192</v>
+        <v>1.92</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>

--- a/data/CS7/case33_2/case33_2_operational_data.xlsx
+++ b/data/CS7/case33_2/case33_2_operational_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BF1AD7-FFA8-4ECA-9F99-53B30C515317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E68082A-0F98-0047-9DB6-538B552DDDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38010" yWindow="-12540" windowWidth="23250" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -442,13 +442,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B7BE64-82AA-46B6-895E-9570C0781B75}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -468,15 +468,17 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>4</v>
+        <f>E2*0.75</f>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
-        <v>2.88</v>
+        <f>-F2*0.75</f>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -488,15 +490,17 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" ref="B3:B33" si="0">E3*0.75</f>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C3" s="1">
-        <v>1.92</v>
+        <f t="shared" ref="C3:C33" si="1">-F3*0.75</f>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -508,15 +512,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C4" s="1">
-        <v>3.84</v>
+        <f t="shared" si="1"/>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -528,15 +534,17 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C5" s="1">
-        <v>1.44</v>
+        <f t="shared" si="1"/>
+        <v>-0.89999999999999991</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -548,15 +556,17 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C6" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -568,15 +578,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>4.8</v>
+        <f t="shared" si="1"/>
+        <v>-3</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -588,15 +600,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C8" s="1">
-        <v>4.8</v>
+        <f t="shared" si="1"/>
+        <v>-3</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -608,15 +622,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C9" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -628,15 +644,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C10" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -648,15 +666,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>1.3499999999999999</v>
       </c>
       <c r="C11" s="1">
-        <v>1.44</v>
+        <f t="shared" si="1"/>
+        <v>-0.89999999999999991</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -668,15 +688,17 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C12" s="1">
-        <v>1.6800000000000002</v>
+        <f t="shared" si="1"/>
+        <v>-1.05</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -688,15 +710,17 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C13" s="1">
-        <v>1.6800000000000002</v>
+        <f t="shared" si="1"/>
+        <v>-1.05</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -708,15 +732,17 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C14" s="1">
-        <v>3.84</v>
+        <f t="shared" si="1"/>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -728,15 +754,17 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C15" s="1">
-        <v>0.48</v>
+        <f t="shared" si="1"/>
+        <v>-0.30000000000000004</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -748,15 +776,17 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C16" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -768,15 +798,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C17" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -788,15 +820,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C18" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -808,15 +842,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C19" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -828,15 +864,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C20" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -848,15 +886,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C21" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -868,15 +908,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C22" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -888,15 +930,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C23" s="1">
-        <v>2.4</v>
+        <f t="shared" si="1"/>
+        <v>-1.5</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -908,15 +952,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>12.600000000000001</v>
       </c>
       <c r="C24" s="1">
-        <v>9.6</v>
+        <f t="shared" si="1"/>
+        <v>-6</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -928,15 +974,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>12.600000000000001</v>
       </c>
       <c r="C25" s="1">
-        <v>9.6</v>
+        <f t="shared" si="1"/>
+        <v>-6</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -948,15 +996,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C26" s="1">
-        <v>1.2</v>
+        <f t="shared" si="1"/>
+        <v>-0.75</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -968,15 +1018,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C27" s="1">
-        <v>1.2</v>
+        <f t="shared" si="1"/>
+        <v>-0.75</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -988,15 +1040,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C28" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1008,15 +1062,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C29" s="1">
-        <v>3.3600000000000003</v>
+        <f t="shared" si="1"/>
+        <v>-2.1</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1028,15 +1084,17 @@
         <v>2.8000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>-18</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1048,15 +1106,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="C31" s="1">
-        <v>3.3600000000000003</v>
+        <f t="shared" si="1"/>
+        <v>-2.1</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1068,15 +1128,17 @@
         <v>2.8000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>8.4</v>
+        <f t="shared" si="0"/>
+        <v>6.3000000000000007</v>
       </c>
       <c r="C32" s="1">
-        <v>4.8</v>
+        <f t="shared" si="1"/>
+        <v>-3</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1088,15 +1150,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C33" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1108,11 +1172,11 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
@@ -1125,12 +1189,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD68AE75-D6B1-4AA7-B0E5-5751542FB30D}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1138,7 +1202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1146,7 +1210,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1154,10 +1218,10 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
     </row>
   </sheetData>
@@ -1168,9 +1232,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206E5596-3B52-412C-A9A4-71C002FACF4D}">
   <dimension ref="A1:AA385"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1253,7 +1317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1336,7 +1400,7 @@
         <v>0.30423493001908397</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1419,7 +1483,7 @@
         <v>0.12215315627057644</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1502,7 +1566,7 @@
         <v>0.28807338371711955</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1585,7 +1649,7 @@
         <v>5.140697371227413E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1668,7 +1732,7 @@
         <v>0.31988431141736134</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1751,7 +1815,7 @@
         <v>0.45601221277188941</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1834,7 +1898,7 @@
         <v>0.23212504519623703</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1917,7 +1981,7 @@
         <v>0.16447266993333343</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2000,7 +2064,7 @@
         <v>0.14884669085844837</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2083,7 +2147,7 @@
         <v>0.21182466623223417</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2166,7 +2230,7 @@
         <v>8.8097283050149661E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2249,7 +2313,7 @@
         <v>0.37751283536620156</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2332,7 +2396,7 @@
         <v>0.71253728546098483</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2415,7 +2479,7 @@
         <v>0.29519824892940821</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2498,7 +2562,7 @@
         <v>0.1208807275594246</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2581,7 +2645,7 @@
         <v>0.29717043793976544</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2664,7 +2728,7 @@
         <v>5.090787688011613E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2747,7 +2811,7 @@
         <v>0.33620493955090019</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2830,7 +2894,7 @@
         <v>0.47011568326998909</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2913,7 +2977,7 @@
         <v>0.22743565034378779</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2996,7 +3060,7 @@
         <v>0.16275941295486118</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3079,7 +3143,7 @@
         <v>0.15970009540021024</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3162,7 +3226,7 @@
         <v>0.21390137864627567</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3245,7 +3309,7 @@
         <v>8.3063152590141104E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3328,7 +3392,7 @@
         <v>0.38918849006824902</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3411,7 +3475,7 @@
         <v>0.764493129192515</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3494,7 +3558,7 @@
         <v>0.31025938407886783</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3577,7 +3641,7 @@
         <v>0.12724287111518379</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3660,7 +3724,7 @@
         <v>0.28807338371711955</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3743,7 +3807,7 @@
         <v>5.240516737659013E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3826,7 +3890,7 @@
         <v>0.33620493955090019</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3909,7 +3973,7 @@
         <v>0.47951799693538888</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -3992,7 +4056,7 @@
         <v>0.3164043272198474</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
@@ -4075,7 +4139,7 @@
         <v>0.13497923767898695</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4158,7 +4222,7 @@
         <v>0.32167183731275839</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4</v>
       </c>
@@ -4241,7 +4305,7 @@
         <v>5.1387009838987807E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>5</v>
       </c>
@@ -4324,7 +4388,7 @@
         <v>0.33607437452583194</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -4407,7 +4471,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -4490,7 +4554,7 @@
         <v>0.25360247362045452</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -4573,7 +4637,7 @@
         <v>0.17105157673066676</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>9</v>
       </c>
@@ -4656,7 +4720,7 @@
         <v>0.15480055849278632</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10</v>
       </c>
@@ -4739,7 +4803,7 @@
         <v>0.20949874832850765</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>11</v>
       </c>
@@ -4822,7 +4886,7 @@
         <v>9.1621174372155653E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>12</v>
       </c>
@@ -4905,7 +4969,7 @@
         <v>0.40070846937426924</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>13</v>
       </c>
@@ -4988,7 +5052,7 @@
         <v>0.7796345465085609</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>14</v>
       </c>
@@ -5071,7 +5135,7 @@
         <v>0.32266975944202259</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>15</v>
       </c>
@@ -5154,7 +5218,7 @@
         <v>0.12968593424059532</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>16</v>
       </c>
@@ -5237,7 +5301,7 @@
         <v>0.31851819184890778</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>17</v>
       </c>
@@ -5320,7 +5384,7 @@
         <v>4.9310767017210523E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>18</v>
       </c>
@@ -5403,7 +5467,7 @@
         <v>0.35644251843648839</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>19</v>
       </c>
@@ -5486,7 +5550,7 @@
         <v>0.51336632613082811</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>20</v>
       </c>
@@ -5569,7 +5633,7 @@
         <v>0.23653307635753931</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>21</v>
       </c>
@@ -5652,7 +5716,7 @@
         <v>0.17283336398827787</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>22</v>
       </c>
@@ -5735,7 +5799,7 @@
         <v>0.16286308758095228</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>23</v>
       </c>
@@ -5818,7 +5882,7 @@
         <v>0.213818310149714</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -5901,7 +5965,7 @@
         <v>8.2895348241474168E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>25</v>
       </c>
@@ -5984,7 +6048,7 @@
         <v>0.40880358996768879</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>26</v>
       </c>
@@ -6067,7 +6131,7 @@
         <v>0.81051116221187025</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>27</v>
       </c>
@@ -6150,7 +6214,7 @@
         <v>0.3070061788865846</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>28</v>
       </c>
@@ -6233,7 +6297,7 @@
         <v>0.12703928252139948</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>29</v>
       </c>
@@ -6316,7 +6380,7 @@
         <v>0.30905725545735607</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>30</v>
       </c>
@@ -6399,7 +6463,7 @@
         <v>5.0867949133543484E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>31</v>
       </c>
@@ -6482,7 +6546,7 @@
         <v>0.32589030257050366</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>32</v>
       </c>
@@ -6565,7 +6629,7 @@
         <v>0.47425270128276498</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -6648,7 +6712,7 @@
         <v>0.28043833648293781</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2</v>
       </c>
@@ -6731,7 +6795,7 @@
         <v>0.12594499382980892</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3</v>
       </c>
@@ -6814,7 +6878,7 @@
         <v>0.30014214231916309</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4</v>
       </c>
@@ -6897,7 +6961,7 @@
         <v>5.1357064029058326E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5</v>
       </c>
@@ -6980,7 +7044,7 @@
         <v>0.3134866251890141</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>6</v>
       </c>
@@ -7063,7 +7127,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>7</v>
       </c>
@@ -7146,7 +7210,7 @@
         <v>0.22518474081461215</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -7229,7 +7293,7 @@
         <v>0.1729361594069862</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>9</v>
       </c>
@@ -7312,7 +7376,7 @@
         <v>0.14435028040543274</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10</v>
       </c>
@@ -7395,7 +7459,7 @@
         <v>0.2035178165760681</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>11</v>
       </c>
@@ -7478,7 +7542,7 @@
         <v>7.8112924304466036E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>12</v>
       </c>
@@ -7561,7 +7625,7 @@
         <v>0.38903281467222173</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>13</v>
       </c>
@@ -7644,7 +7708,7 @@
         <v>0.70556035787417926</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>14</v>
       </c>
@@ -7727,7 +7791,7 @@
         <v>0.29224626644011414</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>15</v>
       </c>
@@ -7810,7 +7874,7 @@
         <v>0.13093291437752413</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>16</v>
       </c>
@@ -7893,7 +7957,7 @@
         <v>0.29122702918097015</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>17</v>
       </c>
@@ -7976,7 +8040,7 @@
         <v>5.0378834238028643E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>18</v>
       </c>
@@ -8059,7 +8123,7 @@
         <v>0.33587852698822945</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>19</v>
       </c>
@@ -8142,7 +8206,7 @@
         <v>0.4422848348204057</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>20</v>
       </c>
@@ -8225,7 +8289,7 @@
         <v>0.22748254429231229</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>21</v>
       </c>
@@ -8308,7 +8372,7 @@
         <v>0.17629414308479177</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>22</v>
       </c>
@@ -8391,7 +8455,7 @@
         <v>0.14890871031297273</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>23</v>
       </c>
@@ -8474,7 +8538,7 @@
         <v>0.20555299474182878</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>24</v>
       </c>
@@ -8557,7 +8621,7 @@
         <v>7.8112924304466036E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>25</v>
       </c>
@@ -8640,7 +8704,7 @@
         <v>0.38521876746955291</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>26</v>
       </c>
@@ -8723,7 +8787,7 @@
         <v>0.72010799411900772</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>27</v>
       </c>
@@ -8806,7 +8870,7 @@
         <v>0.29519824892940821</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>28</v>
       </c>
@@ -8889,7 +8953,7 @@
         <v>0.1184631130082361</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>29</v>
       </c>
@@ -8972,7 +9036,7 @@
         <v>0.30311384669856073</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>30</v>
       </c>
@@ -9055,7 +9119,7 @@
         <v>4.9889719342513801E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>31</v>
       </c>
@@ -9138,7 +9202,7 @@
         <v>0.3134866251890141</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>32</v>
       </c>
@@ -9221,7 +9285,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -9304,7 +9368,7 @@
         <v>0.40460512983649527</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>2</v>
       </c>
@@ -9387,7 +9451,7 @@
         <v>0.12531670023913216</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>3</v>
       </c>
@@ -9470,7 +9534,7 @@
         <v>0.29869072399109714</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4</v>
       </c>
@@ -9553,7 +9617,7 @@
         <v>4.4140186966755215E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5</v>
       </c>
@@ -9636,7 +9700,7 @@
         <v>0.31506655879445489</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>6</v>
       </c>
@@ -9719,7 +9783,7 @@
         <v>0.44456052640476812</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>7</v>
       </c>
@@ -9802,7 +9866,7 @@
         <v>0.24397437503436967</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>8</v>
       </c>
@@ -9885,7 +9949,7 @@
         <v>0.15382663214631914</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>9</v>
       </c>
@@ -9968,7 +10032,7 @@
         <v>0.14269317780774657</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10</v>
       </c>
@@ -10051,7 +10115,7 @@
         <v>0.21685736810291287</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>11</v>
       </c>
@@ -10134,7 +10198,7 @@
         <v>7.9818120109252197E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>12</v>
       </c>
@@ -10217,7 +10281,7 @@
         <v>0.45025918839909279</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>13</v>
       </c>
@@ -10300,7 +10364,7 @@
         <v>0.78440506467065618</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>14</v>
       </c>
@@ -10383,7 +10447,7 @@
         <v>0.4349917738149664</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>15</v>
       </c>
@@ -10466,7 +10530,7 @@
         <v>0.12151477012193317</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>16</v>
       </c>
@@ -10549,7 +10613,7 @@
         <v>0.29988121067334794</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>17</v>
       </c>
@@ -10632,7 +10696,7 @@
         <v>4.4687934013653223E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>18</v>
       </c>
@@ -10715,7 +10779,7 @@
         <v>0.33018527981719359</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>19</v>
       </c>
@@ -10798,7 +10862,7 @@
         <v>0.42311155071818235</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>20</v>
       </c>
@@ -10881,7 +10945,7 @@
         <v>0.23439270222739572</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>21</v>
       </c>
@@ -10964,7 +11028,7 @@
         <v>0.15708373083840152</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>22</v>
       </c>
@@ -11047,7 +11111,7 @@
         <v>0.14033793264830885</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>23</v>
       </c>
@@ -11130,7 +11194,7 @@
         <v>0.19882125121158906</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>24</v>
       </c>
@@ -11213,7 +11277,7 @@
         <v>7.9720383742063805E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>25</v>
       </c>
@@ -11296,7 +11360,7 @@
         <v>0.42271478599915069</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>26</v>
       </c>
@@ -11379,7 +11443,7 @@
         <v>0.7719433123864361</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>27</v>
       </c>
@@ -11462,7 +11526,7 @@
         <v>0.42260815392379569</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>28</v>
       </c>
@@ -11545,7 +11609,7 @@
         <v>0.12503041680988139</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>29</v>
       </c>
@@ -11628,7 +11692,7 @@
         <v>0.30983513447948846</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>30</v>
       </c>
@@ -11711,7 +11775,7 @@
         <v>4.7369169177349381E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>31</v>
       </c>
@@ -11794,7 +11858,7 @@
         <v>0.29376889231153613</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>32</v>
       </c>
@@ -11877,7 +11941,7 @@
         <v>0.40276293406267627</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1</v>
       </c>
@@ -11960,7 +12024,7 @@
         <v>0.42689047219041887</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>2</v>
       </c>
@@ -12043,7 +12107,7 @@
         <v>0.12033783871790973</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>3</v>
       </c>
@@ -12126,7 +12190,7 @@
         <v>0.29665445719231714</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4</v>
       </c>
@@ -12209,7 +12273,7 @@
         <v>4.2953112347665981E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5</v>
       </c>
@@ -12292,7 +12356,7 @@
         <v>0.3215536643614364</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>6</v>
       </c>
@@ -12375,7 +12439,7 @@
         <v>0.44732388733607209</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>7</v>
       </c>
@@ -12458,7 +12522,7 @@
         <v>0.21766051836345818</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>8</v>
       </c>
@@ -12541,7 +12605,7 @@
         <v>0.13917647670381256</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>9</v>
       </c>
@@ -12624,7 +12688,7 @@
         <v>0.13581314695342595</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10</v>
       </c>
@@ -12707,7 +12771,7 @@
         <v>0.18744030886223878</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>11</v>
       </c>
@@ -12790,7 +12854,7 @@
         <v>7.5711443802736714E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>12</v>
       </c>
@@ -12873,7 +12937,7 @@
         <v>0.45877795420658402</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>13</v>
       </c>
@@ -12956,7 +13020,7 @@
         <v>0.72691636268398796</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>14</v>
       </c>
@@ -13039,7 +13103,7 @@
         <v>0.40804281413635179</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>15</v>
       </c>
@@ -13122,7 +13186,7 @@
         <v>0.11968020682142257</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>16</v>
       </c>
@@ -13205,7 +13269,7 @@
         <v>0.2817710283800931</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>17</v>
       </c>
@@ -13288,7 +13352,7 @@
         <v>4.7180765681348061E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>18</v>
       </c>
@@ -13371,7 +13435,7 @@
         <v>0.3246823184506501</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>19</v>
       </c>
@@ -13454,7 +13518,7 @@
         <v>0.4378654235287498</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>20</v>
       </c>
@@ -13537,7 +13601,7 @@
         <v>0.2315525622208352</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>21</v>
       </c>
@@ -13620,7 +13684,7 @@
         <v>0.15065394992841988</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>22</v>
       </c>
@@ -13703,7 +13767,7 @@
         <v>0.13333519255883414</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>23</v>
       </c>
@@ -13786,7 +13850,7 @@
         <v>0.2201848013021738</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>24</v>
       </c>
@@ -13869,7 +13933,7 @@
         <v>7.5208128585683348E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>25</v>
       </c>
@@ -13952,7 +14016,7 @@
         <v>0.42885448722957481</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>26</v>
       </c>
@@ -14035,7 +14099,7 @@
         <v>0.75957708235256871</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>27</v>
       </c>
@@ -14118,7 +14182,7 @@
         <v>0.41003335984872546</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>28</v>
       </c>
@@ -14201,7 +14265,7 @@
         <v>0.12746094767742908</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>29</v>
       </c>
@@ -14284,7 +14348,7 @@
         <v>0.31004400592124742</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>30</v>
       </c>
@@ -14367,7 +14431,7 @@
         <v>4.6176909736852456E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31</v>
       </c>
@@ -14450,7 +14514,7 @@
         <v>0.31071405402795677</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>32</v>
       </c>
@@ -14533,7 +14597,7 @@
         <v>0.44091942255282457</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1</v>
       </c>
@@ -14616,7 +14680,7 @@
         <v>0.42965036203221812</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>2</v>
       </c>
@@ -14699,7 +14763,7 @@
         <v>0.12289737753343244</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>3</v>
       </c>
@@ -14782,7 +14846,7 @@
         <v>0.28273252588643172</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>4</v>
       </c>
@@ -14865,7 +14929,7 @@
         <v>4.083949069934821E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>5</v>
       </c>
@@ -14948,7 +15012,7 @@
         <v>0.32221764217060544</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>6</v>
       </c>
@@ -15031,7 +15095,7 @@
         <v>0.46171304926561546</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>7</v>
       </c>
@@ -15114,7 +15178,7 @@
         <v>0.24146630603376001</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>8</v>
       </c>
@@ -15197,7 +15261,7 @@
         <v>0.16428246479929443</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>9</v>
       </c>
@@ -15280,7 +15344,7 @@
         <v>0.13144036344599996</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>10</v>
       </c>
@@ -15363,7 +15427,7 @@
         <v>0.19702677154429635</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>11</v>
       </c>
@@ -15446,7 +15510,7 @@
         <v>7.2314319481827663E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>12</v>
       </c>
@@ -15529,7 +15593,7 @@
         <v>0.46001998724932369</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>13</v>
       </c>
@@ -15612,7 +15676,7 @@
         <v>0.72622447296762938</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>14</v>
       </c>
@@ -15695,7 +15759,7 @@
         <v>0.4010627508493424</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>15</v>
       </c>
@@ -15778,7 +15842,7 @@
         <v>0.12537432575955593</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>16</v>
       </c>
@@ -15861,7 +15925,7 @@
         <v>0.31273459745725996</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>17</v>
       </c>
@@ -15944,7 +16008,7 @@
         <v>4.4051037967967832E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>18</v>
       </c>
@@ -16027,7 +16091,7 @@
         <v>0.29278258429582177</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>19</v>
       </c>
@@ -16110,7 +16174,7 @@
         <v>0.43040774612253258</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>20</v>
       </c>
@@ -16193,7 +16257,7 @@
         <v>0.22549174696111235</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>21</v>
       </c>
@@ -16276,7 +16340,7 @@
         <v>0.14289138994230252</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>22</v>
       </c>
@@ -16359,7 +16423,7 @@
         <v>0.13544434056330421</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>23</v>
       </c>
@@ -16442,7 +16506,7 @@
         <v>0.21582499841669786</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>24</v>
       </c>
@@ -16525,7 +16589,7 @@
         <v>8.3930712813533967E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>25</v>
       </c>
@@ -16608,7 +16672,7 @@
         <v>0.45973303128551724</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>26</v>
       </c>
@@ -16691,7 +16755,7 @@
         <v>0.73190418906602639</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>27</v>
       </c>
@@ -16774,7 +16838,7 @@
         <v>0.39427768777634509</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>28</v>
       </c>
@@ -16857,7 +16921,7 @@
         <v>0.12672797661677199</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>29</v>
       </c>
@@ -16940,7 +17004,7 @@
         <v>0.29363456677379773</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>30</v>
       </c>
@@ -17023,7 +17087,7 @@
         <v>4.8685903486685111E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>31</v>
       </c>
@@ -17106,7 +17170,7 @@
         <v>0.31338468480191034</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>32</v>
       </c>
@@ -17189,7 +17253,7 @@
         <v>0.45918880408260448</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1</v>
       </c>
@@ -17272,7 +17336,7 @@
         <v>0.56850363147764293</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>2</v>
       </c>
@@ -17355,7 +17419,7 @@
         <v>0.1409055153001664</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>3</v>
       </c>
@@ -17438,7 +17502,7 @@
         <v>0.33597021620982936</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>4</v>
       </c>
@@ -17521,7 +17585,7 @@
         <v>4.6885646565674503E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5</v>
       </c>
@@ -17604,7 +17668,7 @@
         <v>0.32717567035626965</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>6</v>
       </c>
@@ -17687,7 +17751,7 @@
         <v>0.45982461493547749</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>7</v>
       </c>
@@ -17770,7 +17834,7 @@
         <v>0.23184769316557399</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>8</v>
       </c>
@@ -17853,7 +17917,7 @@
         <v>0.15918020101075309</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>9</v>
       </c>
@@ -17936,7 +18000,7 @@
         <v>0.13313519014660974</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>10</v>
       </c>
@@ -18019,7 +18083,7 @@
         <v>0.22892824212080104</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>11</v>
       </c>
@@ -18102,7 +18166,7 @@
         <v>7.7288570783292224E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>12</v>
       </c>
@@ -18185,7 +18249,7 @@
         <v>0.55794241306146164</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>13</v>
       </c>
@@ -18268,7 +18332,7 @@
         <v>0.81989931552599016</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>14</v>
       </c>
@@ -18351,7 +18415,7 @@
         <v>0.55226067057828165</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>15</v>
       </c>
@@ -18434,7 +18498,7 @@
         <v>0.13819579385208627</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>16</v>
       </c>
@@ -18517,7 +18581,7 @@
         <v>0.33597021620982936</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>17</v>
       </c>
@@ -18600,7 +18664,7 @@
         <v>4.6425983364050238E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18</v>
       </c>
@@ -18683,7 +18747,7 @@
         <v>0.33699094046695777</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>19</v>
       </c>
@@ -18766,7 +18830,7 @@
         <v>0.4733488683159327</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>20</v>
       </c>
@@ -18849,7 +18913,7 @@
         <v>0.25137170943214865</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>21</v>
       </c>
@@ -18932,7 +18996,7 @@
         <v>0.15454388447645931</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>22</v>
       </c>
@@ -19015,7 +19079,7 @@
         <v>0.13176266241313953</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>23</v>
       </c>
@@ -19098,7 +19162,7 @@
         <v>0.22443945305960886</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>24</v>
       </c>
@@ -19181,7 +19245,7 @@
         <v>8.0542826395220313E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>25</v>
       </c>
@@ -19264,7 +19328,7 @@
         <v>0.56341243671892705</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>26</v>
       </c>
@@ -19347,7 +19411,7 @@
         <v>0.75621781529096177</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>27</v>
       </c>
@@ -19430,7 +19494,7 @@
         <v>0.52518906907934626</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>28</v>
       </c>
@@ -19513,7 +19577,7 @@
         <v>0.14226037602420646</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>29</v>
       </c>
@@ -19596,7 +19660,7 @@
         <v>0.30717276910612967</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>30</v>
       </c>
@@ -19679,7 +19743,7 @@
         <v>4.5046993759177457E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>31</v>
       </c>
@@ -19762,7 +19826,7 @@
         <v>0.33044742705983238</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>32</v>
       </c>
@@ -19845,7 +19909,7 @@
         <v>0.46884078385578098</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>1</v>
       </c>
@@ -19928,7 +19992,7 @@
         <v>0.53601770967892048</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>2</v>
       </c>
@@ -20011,7 +20075,7 @@
         <v>0.13006662950784589</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>3</v>
       </c>
@@ -20094,7 +20158,7 @@
         <v>0.31037248545098522</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>4</v>
       </c>
@@ -20177,7 +20241,7 @@
         <v>4.5506656960801722E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>5</v>
       </c>
@@ -20260,7 +20324,7 @@
         <v>0.33699094046695777</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>6</v>
       </c>
@@ -20343,7 +20407,7 @@
         <v>0.450808446015174</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>7</v>
       </c>
@@ -20426,7 +20490,7 @@
         <v>0.24405020333218316</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>8</v>
       </c>
@@ -20509,7 +20573,7 @@
         <v>0.15454388447645931</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>9</v>
       </c>
@@ -20592,7 +20656,7 @@
         <v>0.14137035654743096</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>10</v>
       </c>
@@ -20675,7 +20739,7 @@
         <v>0.22892824212080104</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>11</v>
       </c>
@@ -20758,7 +20822,7 @@
         <v>8.0542826395220313E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>12</v>
       </c>
@@ -20841,7 +20905,7 @@
         <v>0.53606231843160046</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>13</v>
       </c>
@@ -20924,7 +20988,7 @@
         <v>0.78009837787909742</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>14</v>
       </c>
@@ -21007,7 +21071,7 @@
         <v>0.52518906907934626</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>15</v>
       </c>
@@ -21090,7 +21154,7 @@
         <v>0.1409055153001664</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>16</v>
       </c>
@@ -21173,7 +21237,7 @@
         <v>0.30397305276127418</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>17</v>
       </c>
@@ -21256,7 +21320,7 @@
         <v>4.5046993759177457E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>18</v>
       </c>
@@ -21339,7 +21403,7 @@
         <v>0.32390391365270693</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>19</v>
       </c>
@@ -21422,7 +21486,7 @@
         <v>0.4282680237144153</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>20</v>
       </c>
@@ -21505,7 +21569,7 @@
         <v>0.23916919926553951</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>21</v>
       </c>
@@ -21588,7 +21652,7 @@
         <v>0.15918020101075309</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>22</v>
       </c>
@@ -21671,7 +21735,7 @@
         <v>0.13999782881396075</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>23</v>
       </c>
@@ -21754,7 +21818,7 @@
         <v>0.2177062694678206</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>24</v>
       </c>
@@ -21837,7 +21901,7 @@
         <v>8.1356390298202338E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>25</v>
       </c>
@@ -21920,7 +21984,7 @@
         <v>0.54700236574653105</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>26</v>
       </c>
@@ -22003,7 +22067,7 @@
         <v>0.79601875293785451</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>27</v>
       </c>
@@ -22086,7 +22150,7 @@
         <v>0.5197747487795592</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>28</v>
       </c>
@@ -22169,7 +22233,7 @@
         <v>0.13006662950784589</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>29</v>
       </c>
@@ -22252,7 +22316,7 @@
         <v>0.31997163448555177</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>30</v>
       </c>
@@ -22335,7 +22399,7 @@
         <v>4.7345309767298761E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>31</v>
       </c>
@@ -22418,7 +22482,7 @@
         <v>0.31736040024558154</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>32</v>
       </c>
@@ -22501,7 +22565,7 @@
         <v>0.4282680237144153</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>1</v>
       </c>
@@ -22584,7 +22648,7 @@
         <v>0.52979124133416533</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>2</v>
       </c>
@@ -22667,7 +22731,7 @@
         <v>0.1299988864716439</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>3</v>
       </c>
@@ -22750,7 +22814,7 @@
         <v>0.30701278328888693</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>4</v>
       </c>
@@ -22833,7 +22897,7 @@
         <v>4.1921283988132489E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>5</v>
       </c>
@@ -22916,7 +22980,7 @@
         <v>0.31081688683845615</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>6</v>
       </c>
@@ -22999,7 +23063,7 @@
         <v>0.41970266324012701</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>7</v>
       </c>
@@ -23082,7 +23146,7 @@
         <v>0.23416617009722973</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>8</v>
       </c>
@@ -23165,7 +23229,7 @@
         <v>0.14975302405768906</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>9</v>
       </c>
@@ -23248,7 +23312,7 @@
         <v>0.13169403602646604</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>10</v>
       </c>
@@ -23331,7 +23395,7 @@
         <v>0.20682095599442957</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>11</v>
       </c>
@@ -23414,7 +23478,7 @@
         <v>7.9607227906790992E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>12</v>
       </c>
@@ -23497,7 +23561,7 @@
         <v>0.51965224745920446</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>13</v>
       </c>
@@ -23580,7 +23644,7 @@
         <v>0.76377999344387137</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>14</v>
       </c>
@@ -23663,7 +23727,7 @@
         <v>0.52979124133416533</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>15</v>
       </c>
@@ -23746,7 +23810,7 @@
         <v>0.13257312184732001</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>16</v>
       </c>
@@ -23829,7 +23893,7 @@
         <v>0.30397305276127418</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>17</v>
       </c>
@@ -23912,7 +23976,7 @@
         <v>4.1484603946589441E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>18</v>
       </c>
@@ -23995,7 +24059,7 @@
         <v>0.32324956231199442</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>19</v>
       </c>
@@ -24078,7 +24142,7 @@
         <v>0.44968142490013607</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>20</v>
       </c>
@@ -24161,7 +24225,7 @@
         <v>0.23648464702888547</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>21</v>
       </c>
@@ -24244,7 +24308,7 @@
         <v>0.15122119096021541</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>22</v>
       </c>
@@ -24327,7 +24391,7 @@
         <v>0.13169403602646604</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>23</v>
       </c>
@@ -24410,7 +24474,7 @@
         <v>0.21748183001476099</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>24</v>
       </c>
@@ -24493,7 +24557,7 @@
         <v>7.5742799367626373E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>25</v>
       </c>
@@ -24576,7 +24640,7 @@
         <v>0.5300452924083886</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>26</v>
       </c>
@@ -24659,7 +24723,7 @@
         <v>0.77134217159678098</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>27</v>
       </c>
@@ -24742,7 +24806,7 @@
         <v>0.50921682419497438</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>28</v>
       </c>
@@ -24825,7 +24889,7 @@
         <v>0.13386023953515808</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>29</v>
       </c>
@@ -24908,7 +24972,7 @@
         <v>0.29789359170604868</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>30</v>
       </c>
@@ -24991,7 +25055,7 @@
         <v>4.4978044278933815E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>31</v>
       </c>
@@ -25074,7 +25138,7 @@
         <v>0.31392505570684071</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>32</v>
       </c>
@@ -25157,7 +25221,7 @@
         <v>0.40685462252869453</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>1</v>
       </c>
@@ -25240,7 +25304,7 @@
         <v>0.38991367175680802</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>2</v>
       </c>
@@ -25323,7 +25387,7 @@
         <v>0.12626746373434408</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>3</v>
       </c>
@@ -25406,7 +25470,7 @@
         <v>0.29748174575997999</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>4</v>
       </c>
@@ -25489,7 +25553,7 @@
         <v>4.5989104722610467E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>5</v>
       </c>
@@ -25572,7 +25636,7 @@
         <v>0.29758364319182595</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>6</v>
       </c>
@@ -25655,7 +25719,7 @@
         <v>0.46963632109024683</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>7</v>
       </c>
@@ -25738,7 +25802,7 @@
         <v>0.23346439779015135</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>8</v>
       </c>
@@ -25821,7 +25885,7 @@
         <v>0.1479600323897812</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>9</v>
       </c>
@@ -25904,7 +25968,7 @@
         <v>0.14914807358193835</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>10</v>
       </c>
@@ -25987,7 +26051,7 @@
         <v>0.21630483374172366</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>11</v>
       </c>
@@ -26070,7 +26134,7 @@
         <v>7.7467480970060482E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>12</v>
       </c>
@@ -26153,7 +26217,7 @@
         <v>0.42050493603836914</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>13</v>
       </c>
@@ -26236,7 +26300,7 @@
         <v>0.71913619665267769</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>14</v>
       </c>
@@ -26319,7 +26383,7 @@
         <v>0.38462437459764404</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>15</v>
       </c>
@@ -26402,7 +26466,7 @@
         <v>0.11771851435202564</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>16</v>
       </c>
@@ -26485,7 +26549,7 @@
         <v>0.30105279375407817</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>17</v>
       </c>
@@ -26568,7 +26632,7 @@
         <v>4.6766775035971847E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>18</v>
       </c>
@@ -26651,7 +26715,7 @@
         <v>0.30864966612628669</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>19</v>
       </c>
@@ -26734,7 +26798,7 @@
         <v>0.46092865073350575</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>20</v>
       </c>
@@ -26817,7 +26881,7 @@
         <v>0.22107520885198301</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>21</v>
       </c>
@@ -26900,7 +26964,7 @@
         <v>0.14942932593407893</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>22</v>
       </c>
@@ -26983,7 +27047,7 @@
         <v>0.14580624846449972</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>23</v>
       </c>
@@ -27066,7 +27130,7 @@
         <v>0.20833483292938207</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>24</v>
       </c>
@@ -27149,7 +27213,7 @@
         <v>7.6075164377009091E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>25</v>
       </c>
@@ -27232,7 +27296,7 @@
         <v>0.46772855744554459</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>26</v>
       </c>
@@ -27315,7 +27379,7 @@
         <v>0.69763343251953736</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>27</v>
       </c>
@@ -27398,7 +27462,7 @@
         <v>0.38316213563756696</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>28</v>
       </c>
@@ -27481,7 +27545,7 @@
         <v>0.1289304828276106</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>29</v>
       </c>
@@ -27564,7 +27628,7 @@
         <v>0.28713789806851081</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>30</v>
       </c>
@@ -27647,7 +27711,7 @@
         <v>4.4676910970780283E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>31</v>
       </c>
@@ -27730,7 +27794,7 @@
         <v>0.30928644336699423</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>32</v>
       </c>
@@ -27813,7 +27877,7 @@
         <v>0.45203518990861852</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1</v>
       </c>
@@ -27896,7 +27960,7 @@
         <v>0.37538367038182924</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>2</v>
       </c>
@@ -27979,7 +28043,7 @@
         <v>0.12018811300212001</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>3</v>
       </c>
@@ -28062,7 +28126,7 @@
         <v>0.28154725817896198</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>4</v>
       </c>
@@ -28145,7 +28209,7 @@
         <v>4.6882367854616955E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>5</v>
       </c>
@@ -28228,7 +28292,7 @@
         <v>0.30259669914399334</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>6</v>
       </c>
@@ -28311,7 +28375,7 @@
         <v>0.43565833319397973</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>7</v>
       </c>
@@ -28394,7 +28458,7 @@
         <v>0.21772304768995185</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>8</v>
       </c>
@@ -28477,7 +28541,7 @@
         <v>0.16035307422661751</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>9</v>
       </c>
@@ -28560,7 +28624,7 @@
         <v>0.1386796906061204</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>10</v>
       </c>
@@ -28643,7 +28707,7 @@
         <v>0.2130218266585143</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>11</v>
       </c>
@@ -28726,7 +28790,7 @@
         <v>7.7051441060587519E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>12</v>
       </c>
@@ -28809,7 +28873,7 @@
         <v>0.41695009600600685</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>13</v>
       </c>
@@ -28892,7 +28956,7 @@
         <v>0.71830057796525593</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>14</v>
       </c>
@@ -28975,7 +29039,7 @@
         <v>0.35771485362760636</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>15</v>
       </c>
@@ -29058,7 +29122,7 @@
         <v>0.11720366727689044</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>16</v>
       </c>
@@ -29141,7 +29205,7 @@
         <v>0.29742669809320632</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>17</v>
       </c>
@@ -29224,7 +29288,7 @@
         <v>4.3774702556512855E-2</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>18</v>
       </c>
@@ -29307,7 +29371,7 @@
         <v>0.31479827545539374</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>19</v>
       </c>
@@ -29390,7 +29454,7 @@
         <v>0.4436653899862828</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>20</v>
       </c>
@@ -29473,7 +29537,7 @@
         <v>0.23657711677899329</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>21</v>
       </c>
@@ -29556,7 +29620,7 @@
         <v>0.15822983535940957</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>22</v>
       </c>
@@ -29639,7 +29703,7 @@
         <v>0.14485334106993131</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>23</v>
       </c>
@@ -29722,7 +29786,7 @@
         <v>0.20046621042375082</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>24</v>
       </c>
@@ -29805,7 +29869,7 @@
         <v>8.1244140608213222E-2</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>25</v>
       </c>
@@ -29888,7 +29952,7 @@
         <v>0.42038347631675754</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>26</v>
       </c>
@@ -29971,7 +30035,7 @@
         <v>0.76319264462658776</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>27</v>
       </c>
@@ -30054,7 +30118,7 @@
         <v>0.40699492683503591</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>28</v>
       </c>
@@ -30137,7 +30201,7 @@
         <v>0.12384606230212507</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>29</v>
       </c>
@@ -30220,7 +30284,7 @@
         <v>0.29237113682890775</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>30</v>
       </c>
@@ -30303,7 +30367,7 @@
         <v>5.043452388991345E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>31</v>
       </c>
@@ -30386,7 +30450,7 @@
         <v>0.33298126403136252</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>32</v>
       </c>
@@ -30469,7 +30533,7 @@
         <v>0.43966360856781511</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1</v>
       </c>
@@ -30552,7 +30616,7 @@
         <v>0.36542259844303537</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>2</v>
       </c>
@@ -30635,7 +30699,7 @@
         <v>0.11993956495672245</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>3</v>
       </c>
@@ -30718,7 +30782,7 @@
         <v>0.29133395395230999</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>4</v>
       </c>
@@ -30801,7 +30865,7 @@
         <v>4.6491627052506763E-2</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>5</v>
       </c>
@@ -30884,7 +30948,7 @@
         <v>0.33094444964029684</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>6</v>
       </c>
@@ -30967,7 +31031,7 @@
         <v>0.44131775373106019</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>7</v>
       </c>
@@ -31050,7 +31114,7 @@
         <v>0.21940458410267669</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>8</v>
       </c>
@@ -31133,7 +31197,7 @@
         <v>0.14882351390693122</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>9</v>
       </c>
@@ -31216,7 +31280,7 @@
         <v>0.14232419957901937</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>10</v>
       </c>
@@ -31299,7 +31363,7 @@
         <v>0.1987066051117635</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>11</v>
       </c>
@@ -31382,7 +31446,7 @@
         <v>8.2968124911176055E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>12</v>
       </c>
@@ -31465,7 +31529,7 @@
         <v>0.44534195487828471</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>13</v>
       </c>
@@ -31548,7 +31612,7 @@
         <v>0.72046342351678183</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>14</v>
       </c>
@@ -31631,7 +31695,7 @@
         <v>0.3905046989223474</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>15</v>
       </c>
@@ -31714,7 +31778,7 @@
         <v>0.12557691115573524</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>16</v>
       </c>
@@ -31797,7 +31861,7 @@
         <v>0.29689256902968525</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>17</v>
       </c>
@@ -31880,7 +31944,7 @@
         <v>4.5766371175294397E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>18</v>
       </c>
@@ -31963,7 +32027,7 @@
         <v>0.32149215231149958</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>19</v>
       </c>
@@ -32046,7 +32110,7 @@
         <v>0.43026063286055011</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>20</v>
       </c>
@@ -32129,7 +32193,7 @@
         <v>0.21739521351587132</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>21</v>
       </c>
@@ -32212,7 +32276,7 @@
         <v>0.14757998683067833</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>22</v>
       </c>
@@ -32295,7 +32359,7 @@
         <v>0.13246396666318053</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>23</v>
       </c>
@@ -32378,7 +32442,7 @@
         <v>0.19190004695921983</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>24</v>
       </c>
@@ -32461,7 +32525,7 @@
         <v>8.0102468745015948E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>25</v>
       </c>
@@ -32544,7 +32608,7 @@
         <v>0.41896012228240564</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>26</v>
       </c>
@@ -32627,7 +32691,7 @@
         <v>0.68614524604916194</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>27</v>
       </c>
@@ -32710,7 +32774,7 @@
         <v>0.38248935213953739</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>28</v>
       </c>
@@ -32793,7 +32857,7 @@
         <v>0.12614241732230266</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>29</v>
       </c>
@@ -32876,7 +32940,7 @@
         <v>0.30007397257087931</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>30</v>
       </c>
@@ -32959,7 +33023,7 @@
         <v>4.6078634270013533E-2</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>31</v>
       </c>
@@ -33042,7 +33106,7 @@
         <v>0.29177639938549099</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>32</v>
       </c>
@@ -33133,9 +33197,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB35780-D2A8-4868-BC60-ED161DD3DC9F}">
   <dimension ref="A1:AA385"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -33218,7 +33282,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -33301,7 +33365,7 @@
         <v>0.10440066304416196</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -33384,7 +33448,7 @@
         <v>-0.10503458241230207</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -33467,7 +33531,7 @@
         <v>-0.28973750613877669</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -33550,7 +33614,7 @@
         <v>-0.29715603926547057</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -33633,7 +33697,7 @@
         <v>-0.25022140873816789</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -33716,7 +33780,7 @@
         <v>0.22534376338021103</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -33799,7 +33863,7 @@
         <v>-0.22749198791228348</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -33882,7 +33946,7 @@
         <v>-0.72083640057428056</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -33965,7 +34029,7 @@
         <v>-2.726202685746134E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -34048,7 +34112,7 @@
         <v>-0.28544317332426927</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -34131,7 +34195,7 @@
         <v>-0.17665658184026775</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -34214,7 +34278,7 @@
         <v>0.29053667590828686</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -34297,7 +34361,7 @@
         <v>0.16425412952137319</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -34380,7 +34444,7 @@
         <v>0.10239295798562037</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -34463,7 +34527,7 @@
         <v>-0.10503458241230207</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -34546,7 +34610,7 @@
         <v>-0.27318107721656087</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -34629,7 +34693,7 @@
         <v>-0.32843562234604645</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -34712,7 +34776,7 @@
         <v>-0.26827862380174705</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -34795,7 +34859,7 @@
         <v>0.2392825528676468</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -34878,7 +34942,7 @@
         <v>-0.21882562646800599</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -34961,7 +35025,7 @@
         <v>-0.75118740691425023</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -35044,7 +35108,7 @@
         <v>-2.4902812994796415E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -35127,7 +35191,7 @@
         <v>-0.30309945208659528</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -35210,7 +35274,7 @@
         <v>-0.17308776200511083</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -35293,7 +35357,7 @@
         <v>0.27925369820311069</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -35376,7 +35440,7 @@
         <v>0.16267476289135999</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -35459,7 +35523,7 @@
         <v>9.9381400397808003E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -35542,7 +35606,7 @@
         <v>-0.10003293563076388</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -35625,7 +35689,7 @@
         <v>-0.27318107721656087</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -35708,7 +35772,7 @@
         <v>-0.32843562234604645</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -35791,7 +35855,7 @@
         <v>-0.25796021519398754</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -35874,7 +35938,7 @@
         <v>0.2346362897051682</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -35957,7 +36021,7 @@
         <v>0.10546474672518899</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
@@ -36040,7 +36104,7 @@
         <v>-9.9942905988696193E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -36123,7 +36187,7 @@
         <v>-0.2842186964980381</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4</v>
       </c>
@@ -36206,7 +36270,7 @@
         <v>-0.3060707204434347</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>5</v>
       </c>
@@ -36289,7 +36353,7 @@
         <v>-0.26569902164980719</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -36372,7 +36436,7 @@
         <v>0.24646102945367621</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -36455,7 +36519,7 @@
         <v>-0.21869563104634182</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -36538,7 +36602,7 @@
         <v>-0.75027687672405119</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>9</v>
       </c>
@@ -36621,7 +36685,7 @@
         <v>-2.5919896304478624E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10</v>
       </c>
@@ -36704,7 +36768,7 @@
         <v>-0.30916144112832716</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>11</v>
       </c>
@@ -36787,7 +36851,7 @@
         <v>-0.18747010594079325</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>12</v>
       </c>
@@ -36870,7 +36934,7 @@
         <v>0.29053667590828686</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>13</v>
       </c>
@@ -36953,7 +37017,7 @@
         <v>0.15454102474679199</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>14</v>
       </c>
@@ -37036,7 +37100,7 @@
         <v>0.10753268293548682</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>15</v>
       </c>
@@ -37119,7 +37183,7 @@
         <v>-0.10715528064767427</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>16</v>
       </c>
@@ -37202,7 +37266,7 @@
         <v>-0.27284994863811657</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>17</v>
       </c>
@@ -37285,7 +37349,7 @@
         <v>-0.31895790867263196</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>18</v>
       </c>
@@ -37368,7 +37432,7 @@
         <v>-0.26038504121681105</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>19</v>
       </c>
@@ -37451,7 +37515,7 @@
         <v>0.22731842522426446</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>20</v>
       </c>
@@ -37534,7 +37598,7 @@
         <v>-0.22762198333394762</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>21</v>
       </c>
@@ -37617,7 +37681,7 @@
         <v>-0.75027687672405119</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>22</v>
       </c>
@@ -37700,7 +37764,7 @@
         <v>-2.7539889823508541E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>23</v>
       </c>
@@ -37783,7 +37847,7 @@
         <v>-0.29703746304486339</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -37866,7 +37930,7 @@
         <v>-0.17644245265015834</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>25</v>
       </c>
@@ -37949,7 +38013,7 @@
         <v>0.27891520887195537</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>26</v>
       </c>
@@ -38032,7 +38096,7 @@
         <v>0.16592825814918719</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>27</v>
       </c>
@@ -38115,7 +38179,7 @@
         <v>0.10029490619944442</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>28</v>
       </c>
@@ -38198,7 +38262,7 @@
         <v>-0.10715528064767427</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>29</v>
       </c>
@@ -38281,7 +38345,7 @@
         <v>-0.27284994863811657</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>30</v>
       </c>
@@ -38364,7 +38428,7 @@
         <v>-0.32217970572993126</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>31</v>
       </c>
@@ -38447,7 +38511,7 @@
         <v>-0.25772805100031299</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>32</v>
       </c>
@@ -38530,7 +38594,7 @@
         <v>0.23210407628161739</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -38613,7 +38677,7 @@
         <v>0.10329642526196409</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2</v>
       </c>
@@ -38696,7 +38760,7 @@
         <v>-9.9012599687330088E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3</v>
       </c>
@@ -38779,7 +38843,7 @@
         <v>-0.26230902222430585</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4</v>
       </c>
@@ -38862,7 +38926,7 @@
         <v>-0.30347451504774686</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5</v>
       </c>
@@ -38945,7 +39009,7 @@
         <v>-0.25280101089010776</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>6</v>
       </c>
@@ -39028,7 +39092,7 @@
         <v>0.23677357075990837</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>7</v>
       </c>
@@ -39111,7 +39175,7 @@
         <v>-0.21869563104634185</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -39194,7 +39258,7 @@
         <v>-0.75847164843584303</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>9</v>
       </c>
@@ -39277,7 +39341,7 @@
         <v>-2.5175433263371027E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10</v>
       </c>
@@ -39360,7 +39424,7 @@
         <v>-0.29703746304486334</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>11</v>
       </c>
@@ -39443,7 +39507,7 @@
         <v>-0.17662089364191619</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>12</v>
       </c>
@@ -39526,7 +39590,7 @@
         <v>0.26813996516351213</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>13</v>
       </c>
@@ -39609,7 +39673,7 @@
         <v>0.14703903325422923</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>14</v>
       </c>
@@ -39692,7 +39756,7 @@
         <v>9.7393772389851849E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>15</v>
       </c>
@@ -39775,7 +39839,7 @@
         <v>-0.10195356799487455</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>16</v>
       </c>
@@ -39858,7 +39922,7 @@
         <v>-0.27853432256807731</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>17</v>
       </c>
@@ -39941,7 +40005,7 @@
         <v>-0.30960531333153979</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>18</v>
       </c>
@@ -40024,7 +40088,7 @@
         <v>-0.25280101089010776</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>19</v>
       </c>
@@ -40107,7 +40171,7 @@
         <v>0.23222023286067936</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>20</v>
       </c>
@@ -40190,7 +40254,7 @@
         <v>-0.21444911393864588</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>21</v>
       </c>
@@ -40273,7 +40337,7 @@
         <v>-0.72872766222267271</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>22</v>
       </c>
@@ -40356,7 +40420,7 @@
         <v>-2.5689217615684722E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>23</v>
       </c>
@@ -40439,7 +40503,7 @@
         <v>-0.29703746304486334</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>24</v>
       </c>
@@ -40522,7 +40586,7 @@
         <v>-0.17137472848423552</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>25</v>
       </c>
@@ -40605,7 +40669,7 @@
         <v>0.26813996516351213</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>26</v>
       </c>
@@ -40688,7 +40752,7 @@
         <v>0.14703903325422923</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>27</v>
       </c>
@@ -40771,7 +40835,7 @@
         <v>0.10231264978327871</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>28</v>
       </c>
@@ -40854,7 +40918,7 @@
         <v>-9.6071631379785624E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>29</v>
       </c>
@@ -40937,7 +41001,7 @@
         <v>-0.27042167239619158</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>30</v>
       </c>
@@ -41020,7 +41084,7 @@
         <v>-0.31573611161533266</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>31</v>
       </c>
@@ -41103,7 +41167,7 @@
         <v>-0.25785703110790992</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>32</v>
       </c>
@@ -41186,7 +41250,7 @@
         <v>0.22311355706222133</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -41269,7 +41333,7 @@
         <v>0.23760749463551797</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>2</v>
       </c>
@@ -41352,7 +41416,7 @@
         <v>-3.5905771033493038E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>3</v>
       </c>
@@ -41435,7 +41499,7 @@
         <v>-0.20578658689322218</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4</v>
       </c>
@@ -41518,7 +41582,7 @@
         <v>-0.28962811170780051</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5</v>
       </c>
@@ -41601,7 +41665,7 @@
         <v>-0.12389553246065828</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>6</v>
       </c>
@@ -41684,7 +41748,7 @@
         <v>0.33237688508273816</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>7</v>
       </c>
@@ -41767,7 +41831,7 @@
         <v>-0.15590387379103984</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>8</v>
       </c>
@@ -41850,7 +41914,7 @@
         <v>-0.828655542709546</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>9</v>
       </c>
@@ -41933,7 +41997,7 @@
         <v>-1.6089547589897894E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10</v>
       </c>
@@ -42016,7 +42080,7 @@
         <v>-0.15731781796771568</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>11</v>
       </c>
@@ -42099,7 +42163,7 @@
         <v>-0.13524649072189965</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>12</v>
       </c>
@@ -42182,7 +42246,7 @@
         <v>0.38975295617822353</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>13</v>
       </c>
@@ -42265,7 +42329,7 @@
         <v>0.18031544078576742</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>14</v>
       </c>
@@ -42348,7 +42412,7 @@
         <v>0.22202818712711603</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>15</v>
       </c>
@@ -42431,7 +42495,7 @@
         <v>-3.5986237224313211E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>16</v>
       </c>
@@ -42514,7 +42578,7 @@
         <v>-0.19719024690254594</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>17</v>
       </c>
@@ -42597,7 +42661,7 @@
         <v>-0.26353988069316525</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>18</v>
       </c>
@@ -42680,7 +42744,7 @@
         <v>-0.114817589943775</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>19</v>
       </c>
@@ -42763,7 +42827,7 @@
         <v>0.34470553774825213</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>20</v>
       </c>
@@ -42846,7 +42910,7 @@
         <v>-0.16614510917506134</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>21</v>
       </c>
@@ -42929,7 +42993,7 @@
         <v>-0.75903892741456302</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>22</v>
       </c>
@@ -43012,7 +43076,7 @@
         <v>-1.4912564087038236E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>23</v>
       </c>
@@ -43095,7 +43159,7 @@
         <v>-0.17396207697380037</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>24</v>
       </c>
@@ -43178,7 +43242,7 @@
         <v>-0.13971909935658441</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>25</v>
       </c>
@@ -43261,7 +43325,7 @@
         <v>0.40211757717383378</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>26</v>
       </c>
@@ -43344,7 +43408,7 @@
         <v>0.18313533440208066</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>27</v>
       </c>
@@ -43427,7 +43491,7 @@
         <v>0.22566608737329294</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>28</v>
       </c>
@@ -43510,7 +43574,7 @@
         <v>-3.7456848986658464E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>29</v>
       </c>
@@ -43593,7 +43657,7 @@
         <v>-0.21267994555977024</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>30</v>
       </c>
@@ -43676,7 +43740,7 @@
         <v>-0.2674527790746834</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>31</v>
       </c>
@@ -43759,7 +43823,7 @@
         <v>-0.11245437744379867</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>32</v>
       </c>
@@ -43842,7 +43906,7 @@
         <v>0.3109013348788397</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1</v>
       </c>
@@ -43925,7 +43989,7 @@
         <v>0.2307535183084562</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>2</v>
       </c>
@@ -44008,7 +44072,7 @@
         <v>-3.531095206826363E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>3</v>
       </c>
@@ -44091,7 +44155,7 @@
         <v>-0.2146930384344056</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4</v>
       </c>
@@ -44174,7 +44238,7 @@
         <v>-0.2546406723509716</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5</v>
       </c>
@@ -44257,7 +44321,7 @@
         <v>-0.12220395679471781</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>6</v>
       </c>
@@ -44340,7 +44404,7 @@
         <v>0.30166028657189642</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>7</v>
       </c>
@@ -44423,7 +44487,7 @@
         <v>-0.18167805818432164</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>8</v>
       </c>
@@ -44506,7 +44570,7 @@
         <v>-0.73052453371612514</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>9</v>
       </c>
@@ -44589,7 +44653,7 @@
         <v>-1.5009826760444123E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10</v>
       </c>
@@ -44672,7 +44736,7 @@
         <v>-0.15860070411137861</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>11</v>
       </c>
@@ -44755,7 +44819,7 @@
         <v>-0.13730456798862051</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>12</v>
       </c>
@@ -44838,7 +44902,7 @@
         <v>0.36839082356962832</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>13</v>
       </c>
@@ -44921,7 +44985,7 @@
         <v>0.18245761903417482</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>14</v>
       </c>
@@ -45004,7 +45068,7 @@
         <v>0.22742473480474143</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>15</v>
       </c>
@@ -45087,7 +45151,7 @@
         <v>-3.2943145724916648E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>16</v>
       </c>
@@ -45170,7 +45234,7 @@
         <v>-0.22637920635014494</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>17</v>
       </c>
@@ -45253,7 +45317,7 @@
         <v>-0.26054650878898294</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>18</v>
       </c>
@@ -45336,7 +45400,7 @@
         <v>-0.11699798865364913</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>19</v>
       </c>
@@ -45419,7 +45483,7 @@
         <v>0.34963630090064257</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>20</v>
       </c>
@@ -45502,7 +45566,7 @@
         <v>-0.17279007194861853</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>21</v>
       </c>
@@ -45585,7 +45649,7 @@
         <v>-0.78430854703951447</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>22</v>
       </c>
@@ -45668,7 +45732,7 @@
         <v>-1.5923976692796063E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>23</v>
       </c>
@@ -45751,7 +45815,7 @@
         <v>-0.16803320521638915</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>24</v>
       </c>
@@ -45834,7 +45898,7 @@
         <v>-0.13354300735013738</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>25</v>
       </c>
@@ -45917,7 +45981,7 @@
         <v>0.40066736701528766</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>26</v>
       </c>
@@ -46000,7 +46064,7 @@
         <v>0.18382947054603144</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>27</v>
       </c>
@@ -46083,7 +46147,7 @@
         <v>0.2406992658908256</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>28</v>
       </c>
@@ -46166,7 +46230,7 @@
         <v>-3.5585336327689121E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>29</v>
       </c>
@@ -46249,7 +46313,7 @@
         <v>-0.20896388103592764</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>30</v>
       </c>
@@ -46332,7 +46396,7 @@
         <v>-0.27406735598634852</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31</v>
       </c>
@@ -46415,7 +46479,7 @@
         <v>-0.11233777161752428</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>32</v>
       </c>
@@ -46498,7 +46562,7 @@
         <v>0.32548686065234889</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1</v>
       </c>
@@ -46581,7 +46645,7 @@
         <v>0.21888830163862186</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>2</v>
       </c>
@@ -46664,7 +46728,7 @@
         <v>-3.5272270856435729E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>3</v>
       </c>
@@ -46747,7 +46811,7 @@
         <v>-0.20031496104475072</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>4</v>
       </c>
@@ -46830,7 +46894,7 @@
         <v>-0.28323005944518853</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>5</v>
       </c>
@@ -46913,7 +46977,7 @@
         <v>-0.12143617811566067</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>6</v>
       </c>
@@ -46996,7 +47060,7 @@
         <v>0.33277688952051449</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>7</v>
       </c>
@@ -47079,7 +47143,7 @@
         <v>-0.16502112180551265</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>8</v>
       </c>
@@ -47162,7 +47226,7 @@
         <v>-0.80624253037920024</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>9</v>
       </c>
@@ -47245,7 +47309,7 @@
         <v>-1.5421612694464655E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>10</v>
       </c>
@@ -47328,7 +47392,7 @@
         <v>-0.16208131145492288</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>11</v>
       </c>
@@ -47411,7 +47475,7 @@
         <v>-0.13091245446272495</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>12</v>
       </c>
@@ -47494,7 +47558,7 @@
         <v>0.35947356602414998</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>13</v>
       </c>
@@ -47577,7 +47641,7 @@
         <v>0.16985537032829737</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>14</v>
       </c>
@@ -47660,7 +47724,7 @@
         <v>0.22507598645748134</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>15</v>
       </c>
@@ -47743,7 +47807,7 @@
         <v>-3.1997908184051932E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>16</v>
       </c>
@@ -47826,7 +47890,7 @@
         <v>-0.20988415174255701</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>17</v>
       </c>
@@ -47909,7 +47973,7 @@
         <v>-0.2796749754294815</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>18</v>
       </c>
@@ -47992,7 +48056,7 @@
         <v>-0.11288777572189508</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>19</v>
       </c>
@@ -48075,7 +48139,7 @@
         <v>0.32229740285695407</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>20</v>
       </c>
@@ -48158,7 +48222,7 @@
         <v>-0.16773482769106485</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>21</v>
       </c>
@@ -48241,7 +48305,7 @@
         <v>-0.82928999105755041</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>22</v>
       </c>
@@ -48324,7 +48388,7 @@
         <v>-1.4860788120205935E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>23</v>
       </c>
@@ -48407,7 +48471,7 @@
         <v>-0.16161192709571529</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>24</v>
       </c>
@@ -48490,7 +48554,7 @@
         <v>-0.13035772393242473</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>25</v>
       </c>
@@ -48573,7 +48637,7 @@
         <v>0.36650325620326013</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>26</v>
       </c>
@@ -48656,7 +48720,7 @@
         <v>0.19318789433785161</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>27</v>
       </c>
@@ -48739,7 +48803,7 @@
         <v>0.22473047552438052</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>28</v>
       </c>
@@ -48822,7 +48886,7 @@
         <v>-3.206094483016203E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>29</v>
       </c>
@@ -48905,7 +48969,7 @@
         <v>-0.20327853343157756</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>30</v>
       </c>
@@ -48988,7 +49052,7 @@
         <v>-0.26648446469407749</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>31</v>
       </c>
@@ -49071,7 +49135,7 @@
         <v>-0.1122573573137703</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>32</v>
       </c>
@@ -49154,7 +49218,7 @@
         <v>0.33023862951028665</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1</v>
       </c>
@@ -49237,7 +49301,7 @@
         <v>0.34129538164225937</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>2</v>
       </c>
@@ -49320,7 +49384,7 @@
         <v>5.3833481319321141E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>3</v>
       </c>
@@ -49403,7 +49467,7 @@
         <v>-0.178702442907301</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>4</v>
       </c>
@@ -49486,7 +49550,7 @@
         <v>-0.25843427198662428</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5</v>
       </c>
@@ -49569,7 +49633,7 @@
         <v>-3.3323073312274763E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>6</v>
       </c>
@@ -49652,7 +49716,7 @@
         <v>0.40320032542354517</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>7</v>
       </c>
@@ -49735,7 +49799,7 @@
         <v>-0.15263910926371257</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>8</v>
       </c>
@@ -49818,7 +49882,7 @@
         <v>-0.82565871664279178</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>9</v>
       </c>
@@ -49901,7 +49965,7 @@
         <v>-9.0170305740912161E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>10</v>
       </c>
@@ -49984,7 +50048,7 @@
         <v>-8.9625737462220023E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>11</v>
       </c>
@@ -50067,7 +50131,7 @@
         <v>-0.12162824610174412</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>12</v>
       </c>
@@ -50150,7 +50214,7 @@
         <v>0.46297428949727881</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>13</v>
       </c>
@@ -50233,7 +50297,7 @@
         <v>0.20938376872673248</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>14</v>
       </c>
@@ -50316,7 +50380,7 @@
         <v>0.32791124902883739</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>15</v>
       </c>
@@ -50399,7 +50463,7 @@
         <v>5.6053418693313766E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>16</v>
       </c>
@@ -50482,7 +50546,7 @@
         <v>-0.18246459960008629</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>17</v>
       </c>
@@ -50565,7 +50629,7 @@
         <v>-0.25316010317057075</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18</v>
       </c>
@@ -50648,7 +50712,7 @@
         <v>-3.0784172488482395E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>19</v>
       </c>
@@ -50731,7 +50795,7 @@
         <v>0.42377177059821586</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>20</v>
       </c>
@@ -50814,7 +50878,7 @@
         <v>-0.14522944376547409</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>21</v>
       </c>
@@ -50897,7 +50961,7 @@
         <v>-0.8686617748012706</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>22</v>
       </c>
@@ -50980,7 +51044,7 @@
         <v>-8.7569239229155077E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>23</v>
       </c>
@@ -51063,7 +51127,7 @@
         <v>-9.6027575852378602E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>24</v>
       </c>
@@ -51146,7 +51210,7 @@
         <v>-0.11461123190356658</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>25</v>
       </c>
@@ -51229,7 +51293,7 @@
         <v>0.49604388160422735</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>26</v>
       </c>
@@ -51312,7 +51376,7 @@
         <v>0.20523755548461897</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>27</v>
       </c>
@@ -51395,7 +51459,7 @@
         <v>0.32791124902883739</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>28</v>
       </c>
@@ -51478,7 +51542,7 @@
         <v>5.6608403036811925E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>29</v>
       </c>
@@ -51561,7 +51625,7 @@
         <v>-0.19751322637122745</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>30</v>
       </c>
@@ -51644,7 +51708,7 @@
         <v>-0.27425677843478496</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>31</v>
       </c>
@@ -51727,7 +51791,7 @@
         <v>-3.0784172488482395E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>32</v>
       </c>
@@ -51810,7 +51874,7 @@
         <v>0.4196574815632817</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>1</v>
       </c>
@@ -51893,7 +51957,7 @@
         <v>0.34119500064765867</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>2</v>
       </c>
@@ -51976,7 +52040,7 @@
         <v>5.4876851885097668E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>3</v>
       </c>
@@ -52059,7 +52123,7 @@
         <v>-0.19181355898165775</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>4</v>
       </c>
@@ -52142,7 +52206,7 @@
         <v>-0.28248448178782853</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>5</v>
       </c>
@@ -52225,7 +52289,7 @@
         <v>-3.1053930701010334E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>6</v>
       </c>
@@ -52308,7 +52372,7 @@
         <v>0.43648492371616232</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>7</v>
       </c>
@@ -52391,7 +52455,7 @@
         <v>-0.15569189144898682</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>8</v>
       </c>
@@ -52474,7 +52538,7 @@
         <v>-0.92129751798724857</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>9</v>
       </c>
@@ -52557,7 +52621,7 @@
         <v>-8.4838119391810133E-3</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>10</v>
       </c>
@@ -52640,7 +52704,7 @@
         <v>-9.6082448752865673E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>11</v>
       </c>
@@ -52723,7 +52787,7 @@
         <v>-0.12166333117273501</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>12</v>
       </c>
@@ -52806,7 +52870,7 @@
         <v>0.46713160964786665</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>13</v>
       </c>
@@ -52889,7 +52953,7 @@
         <v>0.21780058160822294</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>14</v>
       </c>
@@ -52972,7 +53036,7 @@
         <v>0.33774858649970252</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>15</v>
       </c>
@@ -53055,7 +53119,7 @@
         <v>5.4876851885097668E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>16</v>
       </c>
@@ -53138,7 +53202,7 @@
         <v>-0.19375106967844216</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>17</v>
       </c>
@@ -53221,7 +53285,7 @@
         <v>-0.26618730014622299</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>18</v>
       </c>
@@ -53304,7 +53368,7 @@
         <v>-3.1707697663136865E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>19</v>
       </c>
@@ -53387,7 +53451,7 @@
         <v>0.43648492371616232</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>20</v>
       </c>
@@ -53470,7 +53534,7 @@
         <v>-0.14653354489316406</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>21</v>
       </c>
@@ -53553,7 +53617,7 @@
         <v>-0.93015614796789525</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>22</v>
       </c>
@@ -53636,7 +53700,7 @@
         <v>-8.4838119391810133E-3</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>23</v>
       </c>
@@ -53719,7 +53783,7 @@
         <v>-9.7024433544560432E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>24</v>
       </c>
@@ -53802,7 +53866,7 @@
         <v>-0.12407250604744263</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>25</v>
       </c>
@@ -53885,7 +53949,7 @@
         <v>0.49632733525085837</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>26</v>
       </c>
@@ -53968,7 +54032,7 @@
         <v>0.21352998196884601</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>27</v>
       </c>
@@ -54051,7 +54115,7 @@
         <v>0.3549806572394833</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>28</v>
       </c>
@@ -54134,7 +54198,7 @@
         <v>5.8878289001719382E-3</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>29</v>
       </c>
@@ -54217,7 +54281,7 @@
         <v>-0.19181355898165775</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>30</v>
       </c>
@@ -54300,7 +54364,7 @@
         <v>-0.28248448178782853</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>31</v>
       </c>
@@ -54383,7 +54447,7 @@
         <v>-3.33421150684532E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>32</v>
       </c>
@@ -54466,7 +54530,7 @@
         <v>0.4068208997742872</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>1</v>
       </c>
@@ -54549,7 +54613,7 @@
         <v>0.33446947400941418</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>2</v>
       </c>
@@ -54632,7 +54696,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>3</v>
       </c>
@@ -54715,7 +54779,7 @@
         <v>-0.182276491765447</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>4</v>
       </c>
@@ -54798,7 +54862,7 @@
         <v>-0.27699934621913286</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>5</v>
       </c>
@@ -54881,7 +54945,7 @@
         <v>-3.2361464625263403E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>6</v>
       </c>
@@ -54964,7 +55028,7 @@
         <v>0.39908603638861101</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>7</v>
       </c>
@@ -55047,7 +55111,7 @@
         <v>-0.15115717616406488</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>8</v>
       </c>
@@ -55130,7 +55194,7 @@
         <v>-0.80914554230993596</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>9</v>
       </c>
@@ -55213,7 +55277,7 @@
         <v>-8.406646965998887E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>10</v>
       </c>
@@ -55296,7 +55360,7 @@
         <v>-8.7824077229561093E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>11</v>
       </c>
@@ -55379,7 +55443,7 @@
         <v>-0.12048213378270846</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>12</v>
       </c>
@@ -55462,7 +55526,7 @@
         <v>0.46769851694112857</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>13</v>
       </c>
@@ -55545,7 +55609,7 @@
         <v>0.1970280532652342</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>14</v>
       </c>
@@ -55628,7 +55692,7 @@
         <v>0.33125728218219291</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>15</v>
       </c>
@@ -55711,7 +55775,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>16</v>
       </c>
@@ -55794,7 +55858,7 @@
         <v>-0.18611389159208799</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>17</v>
       </c>
@@ -55877,7 +55941,7 @@
         <v>-0.25068124382702556</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>18</v>
       </c>
@@ -55960,7 +56024,7 @@
         <v>-3.2688348106326669E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>19</v>
       </c>
@@ -56043,7 +56107,7 @@
         <v>0.39497174735367691</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>20</v>
       </c>
@@ -56126,7 +56190,7 @@
         <v>-0.148178490633773</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>21</v>
       </c>
@@ -56209,7 +56273,7 @@
         <v>-0.85971713870430699</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>22</v>
       </c>
@@ -56292,7 +56356,7 @@
         <v>-8.6667536171745954E-3</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>23</v>
       </c>
@@ -56375,7 +56439,7 @@
         <v>-8.8674607187110732E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>24</v>
       </c>
@@ -56458,7 +56522,7 @@
         <v>-0.1134651195845309</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>25</v>
       </c>
@@ -56541,7 +56605,7 @@
         <v>0.46741506329449761</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>26</v>
       </c>
@@ -56624,7 +56688,7 @@
         <v>0.20731066210567572</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>27</v>
       </c>
@@ -56707,7 +56771,7 @@
         <v>0.33105652019299159</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>28</v>
       </c>
@@ -56790,7 +56854,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>29</v>
       </c>
@@ -56873,7 +56937,7 @@
         <v>-0.18434567794647894</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>30</v>
       </c>
@@ -56956,7 +57020,7 @@
         <v>-0.25068124382702556</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>31</v>
       </c>
@@ -57039,7 +57103,7 @@
         <v>-3.265661184602927E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>32</v>
       </c>
@@ -57122,7 +57186,7 @@
         <v>0.41126433193201606</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>1</v>
       </c>
@@ -57205,7 +57269,7 @@
         <v>0.19741312877482328</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>2</v>
       </c>
@@ -57288,7 +57352,7 @@
         <v>-5.5509142443077385E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>3</v>
       </c>
@@ -57371,7 +57435,7 @@
         <v>-0.23134604557356478</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>4</v>
       </c>
@@ -57454,7 +57518,7 @@
         <v>-0.25544176041861333</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>5</v>
       </c>
@@ -57537,7 +57601,7 @@
         <v>-0.16270967775809597</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>6</v>
       </c>
@@ -57620,7 +57684,7 @@
         <v>0.28175225412934646</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>7</v>
       </c>
@@ -57703,7 +57767,7 @@
         <v>-0.16598751427602706</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>8</v>
       </c>
@@ -57786,7 +57850,7 @@
         <v>-0.78959093885493115</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>9</v>
       </c>
@@ -57869,7 +57933,7 @@
         <v>-1.7461412185552319E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>10</v>
       </c>
@@ -57952,7 +58016,7 @@
         <v>-0.20535899678772981</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>11</v>
       </c>
@@ -58035,7 +58099,7 @@
         <v>-0.15839849252461777</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>12</v>
       </c>
@@ -58118,7 +58182,7 @@
         <v>0.35245854912687019</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>13</v>
       </c>
@@ -58201,7 +58265,7 @@
         <v>0.16081225716204761</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>14</v>
       </c>
@@ -58284,7 +58348,7 @@
         <v>0.18153397104662145</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>15</v>
       </c>
@@ -58367,7 +58431,7 @@
         <v>-5.3909329683069378E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>16</v>
       </c>
@@ -58450,7 +58514,7 @@
         <v>-0.23080100618241389</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>17</v>
       </c>
@@ -58533,7 +58597,7 @@
         <v>-0.27885065903039274</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>18</v>
       </c>
@@ -58616,7 +58680,7 @@
         <v>-0.16569544452305959</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>19</v>
       </c>
@@ -58699,7 +58763,7 @@
         <v>0.28621185639236219</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>20</v>
       </c>
@@ -58782,7 +58846,7 @@
         <v>-0.17556626662073285</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>21</v>
       </c>
@@ -58865,7 +58929,7 @@
         <v>-0.81163218696209283</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>22</v>
       </c>
@@ -58948,7 +59012,7 @@
         <v>-1.8636473990565453E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>23</v>
       </c>
@@ -59031,7 +59095,7 @@
         <v>-0.20315565508373407</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>24</v>
       </c>
@@ -59114,7 +59178,7 @@
         <v>-0.1452795221048481</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>25</v>
       </c>
@@ -59197,7 +59261,7 @@
         <v>0.33261161368040337</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>26</v>
       </c>
@@ -59280,7 +59344,7 @@
         <v>0.15937158615163902</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>27</v>
       </c>
@@ -59363,7 +59427,7 @@
         <v>0.18582768868086444</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>28</v>
       </c>
@@ -59446,7 +59510,7 @@
         <v>-5.5020829672942043E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>29</v>
       </c>
@@ -59529,7 +59593,7 @@
         <v>-0.23222911792352124</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>30</v>
       </c>
@@ -59612,7 +59676,7 @@
         <v>-0.30671134309338133</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>31</v>
       </c>
@@ -59695,7 +59759,7 @@
         <v>-0.14803193051300698</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>32</v>
       </c>
@@ -59778,7 +59842,7 @@
         <v>0.28914801574595983</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1</v>
       </c>
@@ -59861,7 +59925,7 @@
         <v>0.17598171361019971</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>2</v>
       </c>
@@ -59944,7 +60008,7 @@
         <v>-4.9841411421543011E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>3</v>
       </c>
@@ -60027,7 +60091,7 @@
         <v>-0.22467411938961626</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>4</v>
       </c>
@@ -60110,7 +60174,7 @@
         <v>-0.26521910394337467</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>5</v>
       </c>
@@ -60193,7 +60257,7 @@
         <v>-0.15892035534779669</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>6</v>
       </c>
@@ -60276,7 +60340,7 @@
         <v>0.28807906682082157</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>7</v>
       </c>
@@ -60359,7 +60423,7 @@
         <v>-0.18183163125384061</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>8</v>
       </c>
@@ -60442,7 +60506,7 @@
         <v>-0.77397826887815169</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>9</v>
       </c>
@@ -60525,7 +60589,7 @@
         <v>-1.7694522489840651E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>10</v>
       </c>
@@ -60608,7 +60672,7 @@
         <v>-0.21201497421934132</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>11</v>
       </c>
@@ -60691,7 +60755,7 @@
         <v>-0.14546822093702438</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>12</v>
       </c>
@@ -60774,7 +60838,7 @@
         <v>0.33574541709400801</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>13</v>
       </c>
@@ -60857,7 +60921,7 @@
         <v>0.17012409886981447</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>14</v>
       </c>
@@ -60940,7 +61004,7 @@
         <v>0.19069977867171825</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>15</v>
       </c>
@@ -61023,7 +61087,7 @@
         <v>-5.7210265799620144E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>16</v>
       </c>
@@ -61106,7 +61170,7 @@
         <v>-0.21563720722343019</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>17</v>
       </c>
@@ -61189,7 +61253,7 @@
         <v>-0.26837877793199727</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>18</v>
       </c>
@@ -61272,7 +61336,7 @@
         <v>-0.14771910888517525</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>19</v>
       </c>
@@ -61355,7 +61419,7 @@
         <v>0.28083148365021204</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>20</v>
       </c>
@@ -61438,7 +61502,7 @@
         <v>-0.17585624758952306</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>21</v>
       </c>
@@ -61521,7 +61585,7 @@
         <v>-0.78804596031672758</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>22</v>
       </c>
@@ -61604,7 +61668,7 @@
         <v>-1.835223675063001E-2</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>23</v>
       </c>
@@ -61687,7 +61751,7 @@
         <v>-0.21786598903212359</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>24</v>
       </c>
@@ -61770,7 +61834,7 @@
         <v>-0.14572406395195864</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>25</v>
       </c>
@@ -61853,7 +61917,7 @@
         <v>0.31752753790946048</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>26</v>
       </c>
@@ -61936,7 +62000,7 @@
         <v>0.17169500899641987</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>27</v>
       </c>
@@ -62019,7 +62083,7 @@
         <v>0.18796596099810325</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>28</v>
       </c>
@@ -62102,7 +62166,7 @@
         <v>-5.952263758544904E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>29</v>
       </c>
@@ -62185,7 +62249,7 @@
         <v>-0.23767692657785158</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>30</v>
       </c>
@@ -62268,7 +62332,7 @@
         <v>-0.28650404464498619</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>31</v>
       </c>
@@ -62351,7 +62415,7 @@
         <v>-0.15915432150812536</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>32</v>
       </c>
@@ -62434,7 +62498,7 @@
         <v>0.2731966527474296</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1</v>
       </c>
@@ -62517,7 +62581,7 @@
         <v>0.19501476988237185</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>2</v>
       </c>
@@ -62600,7 +62664,7 @@
         <v>-5.0348330939479588E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>3</v>
       </c>
@@ -62683,7 +62747,7 @@
         <v>-0.22990682674428603</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>4</v>
       </c>
@@ -62766,7 +62830,7 @@
         <v>-0.28824220798069622</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>5</v>
       </c>
@@ -62849,7 +62913,7 @@
         <v>-0.16801064454174258</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>6</v>
       </c>
@@ -62932,7 +62996,7 @@
         <v>0.28146715869081351</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>7</v>
       </c>
@@ -63015,7 +63079,7 @@
         <v>-0.19289441956836567</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>8</v>
       </c>
@@ -63098,7 +63162,7 @@
         <v>-0.69388881502398359</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>9</v>
       </c>
@@ -63181,7 +63245,7 @@
         <v>-1.9607210627353693E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>10</v>
       </c>
@@ -63264,7 +63328,7 @@
         <v>-0.20218513468733235</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>11</v>
       </c>
@@ -63347,7 +63411,7 @@
         <v>-0.15405864171055272</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>12</v>
       </c>
@@ -63430,7 +63494,7 @@
         <v>0.35124673238676496</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>13</v>
       </c>
@@ -63513,7 +63577,7 @@
         <v>0.17259242942294106</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>14</v>
       </c>
@@ -63596,7 +63660,7 @@
         <v>0.18638460350136357</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>15</v>
       </c>
@@ -63679,7 +63743,7 @@
         <v>-5.2206519974136147E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>16</v>
       </c>
@@ -63762,7 +63826,7 @@
         <v>-0.22911942200885815</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>17</v>
       </c>
@@ -63845,7 +63909,7 @@
         <v>-0.27316100913376912</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>18</v>
       </c>
@@ -63928,7 +63992,7 @@
         <v>-0.16040620618731405</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>19</v>
       </c>
@@ -64011,7 +64075,7 @@
         <v>0.2995399215497494</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>20</v>
       </c>
@@ -64094,7 +64158,7 @@
         <v>-0.1733083373249055</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>21</v>
       </c>
@@ -64177,7 +64241,7 @@
         <v>-0.74294745728710343</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>22</v>
       </c>
@@ -64260,7 +64324,7 @@
         <v>-1.7942174565296207E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>23</v>
       </c>
@@ -64343,7 +64407,7 @@
         <v>-0.21312340680918018</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>24</v>
       </c>
@@ -64426,7 +64490,7 @@
         <v>-0.14504668087687686</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>25</v>
       </c>
@@ -64509,7 +64573,7 @@
         <v>0.35652131667585779</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>26</v>
       </c>
@@ -64592,7 +64656,7 @@
         <v>0.17599845361741759</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>27</v>
       </c>
@@ -64675,7 +64739,7 @@
         <v>0.17351496840262656</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>28</v>
       </c>
@@ -64758,7 +64822,7 @@
         <v>-5.3810493598558315E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>29</v>
       </c>
@@ -64841,7 +64905,7 @@
         <v>-0.22489861421211996</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>30</v>
       </c>
@@ -64924,7 +64988,7 @@
         <v>-0.27287552780237123</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>31</v>
       </c>
@@ -65007,7 +65071,7 @@
         <v>-0.15444732521633295</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>32</v>
       </c>
@@ -65098,9 +65162,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC7B88F-64DB-4C68-8FFC-305A2A41AB55}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -65183,7 +65247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -65266,7 +65330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -65349,7 +65413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -65432,7 +65496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -65515,7 +65579,7 @@
         <v>0.5335206744279406</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -65598,7 +65662,7 @@
         <v>0.49739060618225611</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -65681,7 +65745,7 @@
         <v>0.40405459654757125</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -65764,7 +65828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -65847,7 +65911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -65930,7 +65994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -66013,7 +66077,7 @@
         <v>0.36852669610598154</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -66096,7 +66160,7 @@
         <v>0.23966278602970695</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -66179,7 +66243,7 @@
         <v>0.30931352870333201</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -66262,7 +66326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -66345,7 +66409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -66428,7 +66492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -66511,7 +66575,7 @@
         <v>0.4676836611802489</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -66594,7 +66658,7 @@
         <v>0.17442794058611</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -66677,7 +66741,7 @@
         <v>0.34263348052990766</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -66760,7 +66824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -66843,7 +66907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -66926,7 +66990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -67009,7 +67073,7 @@
         <v>0.44439983942191891</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -67092,7 +67156,7 @@
         <v>0.50040144520272978</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -67183,9 +67247,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBBB125-439E-474E-9960-563C78F44B33}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -67268,7 +67332,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -67351,7 +67415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -67434,7 +67498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -67517,7 +67581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -67600,7 +67664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -67683,7 +67747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -67766,7 +67830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -67849,7 +67913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -67932,7 +67996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -68015,7 +68079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -68098,7 +68162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -68181,7 +68245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -68264,7 +68328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -68347,7 +68411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -68430,7 +68494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -68513,7 +68577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -68596,7 +68660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -68679,7 +68743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -68762,7 +68826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -68845,7 +68909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -68928,7 +68992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -69011,7 +69075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -69094,7 +69158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -69177,7 +69241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -69268,13 +69332,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D12B52-98C9-449E-BF4A-23F7CAD72921}">
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -69357,7 +69421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -69440,7 +69504,7 @@
         <v>4.5052000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -69523,7 +69587,7 @@
         <v>-9.797600000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -69606,7 +69670,7 @@
         <v>9.4448000000000025</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -69689,7 +69753,7 @@
         <v>4.5052000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -69772,7 +69836,7 @@
         <v>-9.4056960000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -69855,7 +69919,7 @@
         <v>9.4448000000000025</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -69938,7 +70002,7 @@
         <v>4.3249919999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -70021,7 +70085,7 @@
         <v>-9.8759808000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -70104,7 +70168,7 @@
         <v>9.9170400000000036</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -70187,7 +70251,7 @@
         <v>4.2799399999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -70270,7 +70334,7 @@
         <v>-9.6784611839999997</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -70353,7 +70417,7 @@
         <v>10.115380800000004</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -70436,7 +70500,7 @@
         <v>4.1943412000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -70519,7 +70583,7 @@
         <v>-10.06559963136</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -70602,7 +70666,7 @@
         <v>9.7107655680000047</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -70685,7 +70749,7 @@
         <v>4.1104543759999999</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -70768,7 +70832,7 @@
         <v>-10.06559963136</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -70851,7 +70915,7 @@
         <v>9.4194426009600036</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -70934,7 +70998,7 @@
         <v>4.7079339999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -71017,7 +71081,7 @@
         <v>-10.367567620300798</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -71100,7 +71164,7 @@
         <v>9.5136370269696027</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -71183,7 +71247,7 @@
         <v>4.8020926800000003</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -71266,7 +71330,7 @@
         <v>-10.263891944097791</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -71349,7 +71413,7 @@
         <v>9.7990461377786904</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -71432,7 +71496,7 @@
         <v>4.9461554604</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -71515,7 +71579,7 @@
         <v>-10.469169782979748</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -71598,7 +71662,7 @@
         <v>9.5050747536453297</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -71681,7 +71745,7 @@
         <v>4.4725372999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -71764,7 +71828,7 @@
         <v>-10.992628272128735</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -71847,7 +71911,7 @@
         <v>9.6001255011817825</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -71930,7 +71994,7 @@
         <v>4.4725372999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -72013,7 +72077,7 @@
         <v>-10.552923141243587</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -72096,7 +72160,7 @@
         <v>9.888129266217236</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -72179,7 +72243,7 @@
         <v>4.4278119270000005</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -72262,7 +72326,7 @@
         <v>-10.341864678418714</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>18</v>
       </c>

--- a/data/CS7/case33_2/case33_2_operational_data.xlsx
+++ b/data/CS7/case33_2/case33_2_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E68082A-0F98-0047-9DB6-538B552DDDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A33D5E-48B4-484F-BD94-44F8DCA9BB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,12 +473,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*0.75</f>
-        <v>3</v>
+        <f>E2*1</f>
+        <v>4</v>
       </c>
       <c r="C2" s="1">
-        <f>-F2*0.75</f>
-        <v>-1.7999999999999998</v>
+        <f>-F2*1</f>
+        <v>-2.4</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -495,12 +495,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*0.75</f>
-        <v>2.6999999999999997</v>
+        <f t="shared" ref="B3:B33" si="0">E3*1</f>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">-F3*0.75</f>
-        <v>-1.2000000000000002</v>
+        <f t="shared" ref="C3:C33" si="1">-F3*1</f>
+        <v>-1.6</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -518,11 +518,11 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-3.2</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -540,11 +540,11 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>-0.89999999999999991</v>
+        <v>-1.2</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -562,11 +562,11 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-0.8</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -584,11 +584,11 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -606,11 +606,11 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -628,11 +628,11 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-0.8</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-0.8</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -672,11 +672,11 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>1.3499999999999999</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>-0.89999999999999991</v>
+        <v>-1.2</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -694,11 +694,11 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>-1.05</v>
+        <v>-1.4000000000000001</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -716,11 +716,11 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>-1.05</v>
+        <v>-1.4000000000000001</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -738,11 +738,11 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-3.2</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -760,11 +760,11 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>-0.30000000000000004</v>
+        <v>-0.4</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -782,11 +782,11 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-0.8</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -804,11 +804,11 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-0.8</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -826,11 +826,11 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>2.6999999999999997</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.6</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -848,11 +848,11 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>2.6999999999999997</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.6</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -870,11 +870,11 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>2.6999999999999997</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.6</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -892,11 +892,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>2.6999999999999997</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.6</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -914,11 +914,11 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>2.6999999999999997</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.6</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -936,11 +936,11 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>2.6999999999999997</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -958,11 +958,11 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>12.600000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -980,11 +980,11 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>12.600000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1002,11 +1002,11 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>-0.75</v>
+        <v>-1</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1024,11 +1024,11 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>-0.75</v>
+        <v>-1</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1046,11 +1046,11 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-0.8</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>-2.1</v>
+        <v>-2.8000000000000003</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="1"/>
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1112,11 +1112,11 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>-2.1</v>
+        <v>-2.8000000000000003</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="B32" s="1">
         <f t="shared" si="0"/>
-        <v>6.3000000000000007</v>
+        <v>8.4</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1156,11 +1156,11 @@
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.6</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
